--- a/untitled folder/HSC_Physics_2nd_Paper_Chapter_09_Atomic_Model_and_Nuclear_Physics.xlsx
+++ b/untitled folder/HSC_Physics_2nd_Paper_Chapter_09_Atomic_Model_and_Nuclear_Physics.xlsx
@@ -1168,11 +1168,6 @@
           <t>১৯১১ সালে গাইগার ও মার্সডেনের সহায়তায় রাদারফোর্ডের আলফা কণা বিচ্ছুরণ পরীক্ষায় স্বর্ণপাত ব্যবহারের কারণ এবং প্রায় ২০,০০০ আলফা কণার মধ্যে মাত্র একটি কণার বৃহৎ কোণে ($&gt; 90^\circ$ বা $180^\circ$) ফিরে আসার প্রধান ভৌত সিদ্ধান্ত কী ছিল?</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>স্বর্ণ অত্যন্ত নমনীয় ধাতু হওয়ায় এর অতি পাতলা পাত (প্রায় $4 \times 10^{-7}\text{ m}$ বা প্রায় ১০০০টি পরমাণুর পুরুত্ব) তৈরি করা সম্ভব যাতে আলফা কণার একাধিক বিক্ষেপণ না ঘটে। বেশিরভাগ আলফা কণা সরাসরি ভেদ করে যাওয়ায় প্রমাণিত হয় পরমাণুর অধিকাংশ স্থান ফাঁকা। আর ২০,০০০ কণার মধ্যে একটির পেছনের দিকে প্রতিক্ষিপ্ত হওয়া নির্দেশ করে যে পরমাণুর সমগ্র ধনাত্মক আধান এবং প্রায় সমগ্র ভর পরমাণুর কেন্দ্রে অতি ক্ষুদ্র স্থানে কেন্দ্রীভূত, যাকে রাদারফোর্ড 'নিউক্লিয়াস' নামকরণ করেন।</t>
@@ -1218,11 +1213,6 @@
           <t>$K$ গতিশক্তিসম্পন্ন একটি আলফা কণা ($q = 2e$) পারমাণবিক সংখ্যা $Z$-এর একটি স্থির নিউক্লিয়াসের দিকে সরাসরি মস্তকমুখী (Head-on) ধাবিত হলে কণাটির নিকটতম পৌঁছানোর দূরত্ব $r_0$-এর সমীকরণ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>মস্তকমুখী সংঘর্ষে নিকটতম দূরত্বে পৌঁছালে আলফা কণার সমস্ত গতিশক্তি কুলম্ব বিভব শক্তিতে রূপান্তরিত হয়ে কণাটি তাৎক্ষণিকভাবে স্থির হয়: $K = \frac{1}{4\pi\epsilon_0}\frac{(2e)(Ze)}{r_0} = \frac{2 Z e^2}{4\pi\epsilon_0 r_0}$। অতএব নিকটতম দূরত্ব $r_0 = \frac{2 Z e^2}{4\pi\epsilon_0 K} = \frac{1}{4\pi\epsilon_0}\frac{4 Z e^2}{m_\alpha v^2}$। এটি নিউক্লিয়াসের আকারের একটি ঊর্ধ্বসীমা নির্দেশ করে।</t>
@@ -1268,11 +1258,6 @@
           <t>আলফা কণার বিচ্ছুরণে অভিঘাত পরামিতি (Impact parameter) $b$ বলতে কী বোঝায় এবং বিক্ষেপণ কোণ $\theta$-র সাথে এর গাণিতিক সম্পর্কটি কী?</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>অভিঘাত পরামিতি ($b$) হলো নিউক্লিয়াসের কেন্দ্র থেকে আলফা কণার প্রারম্ভিক বেগ ভেক্টরের লম্ব দূরত্ব। রাদারফোর্ডের বিক্ষেপণ সূত্রানুযায়ী: $b = \frac{1}{4\pi\epsilon_0}\frac{Z e^2}{K}\cot\left(\frac{\theta}{2}\right)$। যখন $b = 0$, তখন মস্তকমুখী সংঘর্ষ হয় এবং $\cot(\theta/2) = 0 \Rightarrow \theta = 180^\circ$। $b$ যত বৃদ্ধি পায়, বিক্ষেপণ কোণ $\theta$ তত দ্রুত হ্রাস পেয়ে প্রায় শূন্যে নেমে আসে।</t>
@@ -1318,11 +1303,6 @@
           <t>রাদারফোর্ডের সূত্রানুযায়ী $\theta$ কোণে একক কোণে বিক্ষিপ্ত আলফা কণার সংখ্যা $N(\theta)$ বিক্ষেপণ কোণ $\theta$ এবং কণার গতিশক্তি $K$-এর ওপর কীভাবে নির্ভর করে?</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>রাদারফোর্ডের বিক্ষেপণ সমীকরণ: $N(\theta) \propto \frac{1}{\sin^4(\theta/2)}$ এবং $N(\theta) \propto \frac{1}{K^2}$। অর্থাৎ বিক্ষিপ্ত কণার সংখ্যা অর্ধ-কোণের সাইনের চতুর্থ ঘাতের ব্যস্তানুপাতিক এবং গতিশক্তির বর্গের ব্যস্তানুপাতিক। বিক্ষেপণ কোণ $\theta$ সামান্য বৃদ্ধি পেলেই বিক্ষিপ্ত কণার সংখ্যা নাটকীয়ভাবে হ্রাস পায়।</t>
@@ -1368,11 +1348,6 @@
           <t>ম্যাক্সওয়েলের চিরায়ত তড়িৎগতিবিদ্যা তত্ত্ব প্রয়োগ করলে রাদারফোর্ডের সৌর-সদৃশ পরমাণু মডেল কেন ধ্বংস হয়ে যায়? ইলেকট্রনের আনুমানিক জীবনকাল কত হওয়ার কথা ছিল?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>নিউক্লিয়াসের চারদিকে বৃত্তাকার কক্ষপথে ঘূর্ণায়মান ইলেকট্রন সর্বদা কেন্দ্রমুখী ত্বরণে ($a = v^2/r$) থাকে। ম্যাক্সওয়েলের নীতি অনুযায়ী যেকোনো ত্বরিত আধানযুক্ত কণা অনবরত তড়িৎ-চৌম্বকীয় তরঙ্গ বিকিরণ করে শক্তি হারায়। শক্তি হারালে ইলেকট্রনের কক্ষপথের ব্যাসার্ধ দ্রুত সংকুচিত হতে হতে একটি সর্পিলাকার (Spiral) পথে মাত্র $\sim 10^{-10}\text{ s}$ বা এক সেকেন্ডের একশত কোটি ভাগের এক ভাগে নিউক্লিয়াসে আছড়ে পড়ে পরমাণুটি ধ্বংস হয়ে যাওয়ার কথা। ফলে পরমাণু স্থায়ী হতে পারে না।</t>
@@ -1418,11 +1393,6 @@
           <t>রাদারফোর্ড পরমাণু মডেলে ইলেকট্রনের সর্পিলাকার পতনের ফলে কোন ধরনের বর্ণালী সৃষ্টি হওয়ার কথা ছিল এবং বাস্তব পরমাণুতে কোন ধরনের বর্ণালী পরিলক্ষিত হয়?</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>সর্পিলাকার পথে ব্যাসার্ধ ক্রমাগত অবিচ্ছিন্নভাবে হ্রাস পেলে ইলেকট্রনের আবর্তন কম্পাঙ্ক অবিচ্ছিন্নভাবে বৃদ্ধি পাওয়ার কথা, ফলে একটি অবিচ্ছিন্ন বর্ণালী (Continuous spectrum) তৈরি হওয়ার কথা ছিল। কিন্তু বাস্তবে প্রতিটি মৌলের পরমাণু থেকে কেবল নির্দিষ্ট সুনির্দিষ্ট কম্পাঙ্কের উজ্জ্বল বা অন্ধকার বিচ্ছিন্ন রেখা বর্ণালী (Discrete line spectrum) নির্গত হয়, যা রাদারফোর্ড মডেল ব্যাখ্যা করতে সম্পূর্ণ ব্যর্থ হয়।</t>
@@ -1468,11 +1438,6 @@
           <t>$7.7\text{ MeV}$ গতিশক্তিসম্পন্ন আলফা কণা স্বর্ণের নিউক্লিয়াসে ($Z = 79$) নিক্ষিপ্ত হলে নিকটতম পৌঁছানোর দূরত্ব কত হবে? ($1\text{ eV} = 1.6 \times 10^{-19}\text{ J}, \frac{1}{4\pi\epsilon_0} = 9 \times 10^9\text{ N}\cdot\text{m}^2/\text{C}^2$)</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>গতিশক্তি $K = 7.7 \times 10^6 \times 1.6 \times 10^{-19}\text{ J} \approx 1.232 \times 10^{-12}\text{ J}$। সূত্র: $r_0 = \frac{2 Z e^2}{4\pi\epsilon_0 K} = \frac{2 \times 79 \times (1.6 \times 10^{-19})^2 \times 9 \times 10^9}{1.232 \times 10^{-12}} = \frac{158 \times 2.56 \times 10^{-38} \times 9 \times 10^9}{1.232 \times 10^{-12}} \approx \frac{3.64 \times 10^{-26}}{1.232 \times 10^{-12}} \approx 2.95 \times 10^{-14}\text{ m} \approx 30\text{ fm}$। এটি নির্দেশ করে নিউক্লিয়াসের ব্যাসার্ধ $3 \times 10^{-14}\text{ m}$-এর চেয়ে ছোট।</t>
@@ -1518,11 +1483,6 @@
           <t>আলফা কণার গতিশক্তি অত্যন্ত বৃদ্ধি করলে (যেমন কণা নিউক্লিয়াসের অতি নিকটে গেলে) রাদারফোর্ডের কুলম্বীয় সূত্র থেকে স্পষ্ট বিচ্যুতি লক্ষ্য করা যায় কেন?</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>রাদারফোর্ডের সূত্র কেবল বিশুদ্ধ কুলম্বীয় বৈদ্যুতিক বিকর্ষণ বলের ওপর প্রতিষ্ঠিত। যখন আলফা কণার গতিশক্তি এত বেশি হয় যে এর নিকটতম দূরত্ব নিউক্লিয়াসের প্রকৃত ব্যাসার্ধের সীমানায় পৌঁছে যায় ($r \le 10^{-14}\text{ m}$ বা কয়েক ফেমটোমিটার), তখন কুলম্ব বিকর্ষণকে ছাপিয়ে অত্যন্ত শক্তিশালী কিন্তু স্বল্প-পাল্লার 'তীব্র নিউক্লীয় বল' (Strong Nuclear Force) আলফা কণার ওপর আকর্ষণমূলক প্রভাব ফেলতে শুরু করে। ফলে কণার গতিপথ ক্লাসিক্যাল কুলম্ব সূত্র থেকে বিচ্যুত হয়।</t>
@@ -1568,11 +1528,6 @@
           <t>জে জে থমসনের 'প্লাম পুডিং মডেল' (Plum Pudding Model) কেন আলফা কণার বৃহৎ কোণে বিক্ষেপণ ব্যাখ্যা করতে ব্যর্থ হয়েছিল?</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>থমসনের মডেলে পরমাণুর সমগ্র ধনাত্মক আধান সম্পূর্ণ পারমাণবিক গোলকজুড়ে ($\sim 10^{-10}\text{ m}$) সমসত্ত্বভাবে ছড়িয়ে ছিল। এত বৃহৎ অঞ্চলে বিস্তৃত ধনাত্মক চার্জের পৃষ্ঠে তড়িৎক্ষেত্রের মান অত্যন্ত দুর্বল ($E \sim \frac{Ze}{4\pi\epsilon_0 R^2} \approx$ খুব ছোট) হওয়ায় দ্রুতগামী ভারী আলফা কণাকে সামান্যতম ($&lt; 1^\circ$) বিচ্যুত করা সম্ভব ছিল। কিন্তু ১৮০ ডিগ্রিতে উল্টে আসার জন্য যে প্রচণ্ড কেন্দ্রমুখী বিকর্ষণ প্রয়োজন, তা কেবল একটি ক্ষুদ্র নিউক্লিয়াসের ঘনত্বেই সম্ভব।</t>
@@ -1618,11 +1573,6 @@
           <t>আলফা কণা পরমাণুর মধ্য দিয়ে যাওয়ার সময় কক্ষীয় ইলেকট্রনগুলোর সাথে সংঘর্ষে আলফা কণার কোনো উল্লেখেযোগ্য বিক্ষেপণ ঘটে না কেন?</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>আলফা কণার ভর ($m_\alpha \approx 4\text{ u} \approx 7300 m_e$) ইলেকট্রনের ভরের তুলনায় প্রায় ৭৩০০ গুণ বেশি। ক্লাসিক্যাল বলবিদ্যা অনুসারে একটি ভারী কণা যখন অতি হালকা কণার সাথে সংঘর্ষে লিপ্ত হয়, তখন ভারী কণার গতির দিক প্রায় সম্পূর্ণ অবিকৃত থাকে এবং ইলেকট্রন সামান্য শক্তি গ্রহণ করে ছিটকে যায়। ফলে ইলেকট্রনগুলো আলফা কণার গতিপথে কোনো লক্ষণীয় কৌণিক বিচ্যুতি তৈরি করতে পারে না।</t>
@@ -1668,11 +1618,6 @@
           <t>১৯১৩ সালে নিলস বোর কর্তৃক প্রস্তাবিত বোর পরমাণু মডেলের তিনটি মৌলিক স্বীকার্য (কক্ষপথ, কৌণিক ভরবেগ এবং বিকিরণ সম্পর্কিত) স্পষ্টভাবে বিবৃত করো।</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>(১) স্থায়ী কক্ষপথের স্বীকার্য: পরমাণুর ইলেকট্রন নিউক্লিয়াসকে কেন্দ্র করে কেবল কয়েকটি সুনির্দিষ্ট অনুমোদিত বৃত্তাকার কক্ষপথে কোনো তড়িৎ-চৌম্বকীয় শক্তি বিকিরণ না করে স্থায়ীভাবে ঘোরে। (২) কৌণিক ভরবেগের কোয়ান্টায়ন: অনুমোদিত কক্ষপথে ঘূর্ণায়মান ইলেকট্রনের কক্ষীয় কৌণিক ভরবেগ $L = m v r = \frac{n h}{2\pi} = n\hbar$ ($n = 1, 2, 3, \dots$)। (৩) কম্পাঙ্ক শর্ত (কোয়ান্টাম লাফ): উচ্চ শক্তিস্তর $E_2$ থেকে নিম্ন শক্তিস্তর $E_1$-এ সংক্রমণের সময় পরমাণু একটি নির্দিষ্ট ফোটন আকারে শক্তি বিকিরণ করে: $\Delta E = E_2 - E_1 = h\nu$।</t>
@@ -1718,11 +1663,6 @@
           <t>পারমাণবিক সংখ্যা $Z$ বিশিষ্ট হাইড্রোজেন সদৃশ আয়নের $n$-তম বোর কক্ষপথের ব্যাসার্ধ $r_n$-এর সমীকরণ প্রতিপাদন করো এবং বোর ব্যাসার্ধ $a_0$-এর মান কত?</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>কেন্দ্রমুখী বল কুলম্ব বলের সমান: $\frac{m v^2}{r} = \frac{1}{4\pi\epsilon_0}\frac{Z e^2}{r^2} \Rightarrow v^2 = \frac{Z e^2}{4\pi\epsilon_0 m r}$। বোরের শর্ত: $v = \frac{n h}{2\pi m r}$। বর্গ করে বসালে: $\frac{n^2 h^2}{4\pi^2 m^2 r^2} = \frac{Z e^2}{4\pi\epsilon_0 m r} \Rightarrow r_n = \frac{\epsilon_0 n^2 h^2}{\pi m Z e^2} = \left(\frac{\epsilon_0 h^2}{\pi m e^2}\right)\frac{n^2}{Z} = a_0 \frac{n^2}{Z}$। হাইড্রোজেন ($Z = 1, n = 1$) এর জন্য প্রথম বোর ব্যাসার্ধ $a_0 = \frac{\epsilon_0 h^2}{\pi m e^2} \approx 0.529 \times 10^{-10}\text{ m} = 0.529\text{ \AA}$।</t>
@@ -1768,11 +1708,6 @@
           <t>$n$-তম বোর কক্ষপথে ইলেকট্রনের বেগ $v_n$-এর সমীকরণ কী এবং প্রথম বোর কক্ষপথে হাইড্রোজেনের ইলেকট্রনের বেগ আলোর বেগের কত অংশ?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>কৌণিক ভরবেগ থেকে: $v_n = \frac{n h}{2\pi m r_n} = \frac{n h}{2\pi m} \frac{\pi m Z e^2}{\epsilon_0 n^2 h^2} = \frac{Z e^2}{2 \epsilon_0 n h}$। হাইড্রোজেনের জন্য ($Z = 1, n = 1$): $v_1 = \frac{e^2}{2 \epsilon_0 h} = \frac{e^2}{4\pi\epsilon_0 \hbar c} \cdot c = \alpha c$। এখানে $\alpha = \frac{e^2}{4\pi\epsilon_0 \hbar c} \approx \frac{1}{137}$ হলো সোমারফেল্ডের ফাইন-স্ট্রাকচার ধ্রুবক (Fine-structure constant)। ফলে $v_1 = \frac{c}{137} \approx 2.18 \times 10^6\text{ m/s}$ (আলোর বেগের প্রায় $0.73\%$), যার ফলে অ-আপেক্ষিকীয় হিসাব বেশ নির্ভুল হয়।</t>
@@ -1869,11 +1804,6 @@
           <t>হাইড্রোজেন সদৃশ পরমাণুর $n$-তম স্তরে মোট শক্তি $E_n$-এর রাশিমালাটি প্রতিপাদন করো এবং হাইড্রোজেনের ভূমি অবস্থার শক্তি কত?</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>মোট শক্তি $E_n = -\frac{Z e^2}{8\pi\epsilon_0 r_n} = -\frac{Z e^2}{8\pi\epsilon_0} \frac{\pi m Z e^2}{\epsilon_0 n^2 h^2} = -\frac{m Z^2 e^4}{8 \epsilon_0^2 h^2 n^2} = -\left(\frac{m e^4}{8 \epsilon_0^2 h^2}\right)\frac{Z^2}{n^2}$। ধ্রুবকগুলোর মান বসালে হাইড্রোজেনের জন্য ($Z = 1$): $E_n = -\frac{13.6\text{ eV}}{n^2}$। ভূমি স্তরে ($n = 1$): $E_1 = -13.6\text{ eV}$। এটিই ১ রিডবার্গ শক্তি ($1\text{ Ry} = 13.606\text{ eV}$)।</t>
@@ -1919,11 +1849,6 @@
           <t>হাইড্রোজেন পরমাণু এবং একক আয়নিত হিলিয়াম পরমাণুর ($\text{He}^+$) ক্ষেত্রে ভূমি অবস্থা থেকে একটি ইলেকট্রনকে সম্পূর্ণ মুক্ত করতে প্রয়োজনীয় আয়নায়ন শক্তি (Ionization Energy) যথাক্রমে কত?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>আয়নায়ন শক্তি হলো ভূমি স্তরের ঋণাত্মক শক্তির ধনাত্মক পরম মান: $E_{\text{ion}} = 0 - E_1 = 13.6 \frac{Z^2}{1^2}\text{ eV} = 13.6 Z^2\text{ eV}$। হাইড্রোজেনের জন্য ($Z = 1$): $E_{\text{ion}}(\text{H}) = 13.6 \times 1^2 = 13.6\text{ eV}$। হিলিয়াম আয়নের জন্য ($Z = 2$): $E_{\text{ion}}(\text{He}^+) = 13.6 \times 2^2 = 13.6 \times 4 = 54.4\text{ eV}$।</t>
@@ -1969,11 +1894,6 @@
           <t>$n$-তম বোর কক্ষপথে ইলেকট্রনের আবর্তনের পর্যায়কাল $T_n$ এবং কম্পাঙ্ক $f_n$ প্রধান কোয়ান্টাম সংখ্যা $n$-এর ওপর কীভাবে নির্ভর করে?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>পর্যায়কাল $T_n = \frac{2\pi r_n}{v_n}$। যেহেতু $r_n \propto n^2$ এবং $v_n \propto \frac{1}{n}$, সুতরাং $T_n \propto \frac{n^2}{1/n} = n^3$। কম্পাঙ্ক হলো পর্যায়কালের বিপরীত: $f_n = \frac{1}{T_n} \propto \frac{1}{n^3}$। অর্থাৎ উচ্চতর কক্ষপথে ইলেকট্রনের পর্যায়কাল $n^3$ অনুপাতে দ্রুত বৃদ্ধি পায় এবং ঘূর্ণন কম্পাঙ্ক $n^{-3}$ হারে হ্রাস পায়।</t>
@@ -2019,11 +1939,6 @@
           <t>প্রথম বোর কক্ষপথে ইলেকট্রনের ঘূর্ণনের ফলে সৃষ্ট চৌম্বকীয় দ্বিমেরু ভ্রামক $\mu_B$ (বোর ম্যাগনেটন)-এর সমীকরণ কী এবং এর সাংখ্যিক মান কত?</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>ঘূর্ণায়মান ইলেকট্রনের সমতুল্য তড়িৎ প্রবাহ $I = \frac{e}{T} = \frac{e v}{2\pi r}$। কক্ষীয় ক্ষেত্রফল $A = \pi r^2$। চৌম্বক ভ্রামক $\mu = I A = \left(\frac{e v}{2\pi r}\right)(\pi r^2) = \frac{e v r}{2} = \frac{e (m v r)}{2m} = \frac{e L}{2m}$। প্রথম কক্ষপথে $L = \hbar = \frac{h}{2\pi}$ বসালে বোর ম্যাগনেটন: $\mu_B = \frac{e \hbar}{2m_e} = \frac{e h}{4\pi m_e}$। সাংখ্যিক মান: $\mu_B = \frac{1.602 \times 10^{-19} \times 1.054 \times 10^{-34}}{2 \times 9.109 \times 10^{-31}} \approx 9.274 \times 10^{-24}\text{ A}\cdot\text{m}^2$ (বা $\text{J/T}$)।</t>
@@ -2069,11 +1984,6 @@
           <t>বোরের সঙ্গতি নীতিটি বিবৃত করো এবং দেখাও যে প্রধান কোয়ান্টাম সংখ্যা অত্যন্ত বড় হলে ($n \to \infty$) কোয়ান্টাম বিকিরণ কম্পাঙ্ক চিরায়ত কক্ষীয় ঘূর্ণন কম্পাঙ্কের সমান হয়।</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>সঙ্গতি নীতি অনুসারে: বৃহৎ কোয়ান্টাম সংখ্যার সীমায় ($n \gg 1$) কোয়ান্টাম বলবিদ্যার ফলাফলগুলো চিরায়ত বলবিদ্যার ফলাফলের সাথে একীভূত হয়। স্তর $n$ থেকে $n-1$-এ রূপান্তরে কোয়ান্টাম ফোটন কম্পাঙ্ক $\nu_{\text{quantum}} = \frac{\Delta E}{h} = \frac{m e^4}{8\epsilon_0^2 h^3}\left[\frac{1}{(n-1)^2} - \frac{1}{n^2}\right] \approx \frac{m e^4}{8\epsilon_0^2 h^3}\frac{2n}{n^4} = \frac{m e^4}{4\epsilon_0^2 h^3 n^3}$। চিরায়ত কক্ষীয় কম্পাঙ্ক $f_{\text{classical}} = \frac{v_n}{2\pi r_n} = \frac{m e^4}{4\epsilon_0^2 h^3 n^3}$। ফলে $n \to \infty$ হলে $\nu_{\text{quantum}} = f_{\text{classical}}$।</t>
@@ -2119,11 +2029,6 @@
           <t>নিউক্লিয়াসের ভর $M$ অসীম না হয়ে সসীম বিবেচনা করলে বোর কক্ষপথের শক্তিতে কী সংশোধন ঘটে এবং ভারী হাইড্রোজেনের (ডিউটেরিয়াম) ক্ষেত্রে রিডবার্গ ধ্রুবকের কী পরিবর্তন হয়?</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>নিউক্লিয়াসের সসীম ভরের জন্য ইলেকট্রন ও নিউক্লিয়াস উভয়ই তাদের যৌথ ভরকেন্দ্রকে কেন্দ্র করে ঘোরে। ফলে ইলেকট্রনের ভর $m$-এর স্থানে হ্রাসকৃত ভর $\mu = \frac{m M}{m + M} = \frac{m}{1 + m/M}$ প্রতিস্থাপিত হয়। ডিউটেরিয়ামের নিউক্লিয়াসে প্রোটন ও নিউট্রন উভয়ই থাকায় এর ভর হাইড্রোজেনের দ্বিগুণ ($M_D \approx 2 M_H$), ফলে $\mu_D &gt; \mu_H$। এর দরুন ডিউটেরিয়ামের রিডবার্গ ধ্রুবক $R_D = R_\infty \frac{\mu_D}{m}$ হাইড্রোজেনের $R_H$ অপেক্ষা সামান্য বেশি হয়, যার মাধ্যমে ১৯৩১ সালে হ্যারল্ড ইউরে ডিউটেরিয়াম আবিষ্কার করেছিলেন।</t>
@@ -2169,11 +2074,6 @@
           <t>হাইড্রোজেন বর্ণালীতে $n_2$ স্তর থেকে $n_1$ স্তরে ইলেকট্রন স্থানান্তরিত হলে নির্গত তরঙ্গের তরঙ্গ সংখ্যা $\bar{\nu}$ এবং তরঙ্গদৈর্ঘ্য $\lambda$-এর সমীকরণ লেখো এবং রিডবার্গ ধ্রুবক $R_\infty$-এর তাত্ত্বিক সমীকরণটি দাও।</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>শক্তি পার্থক্য $\Delta E = E_{n_2} - E_{n_1} = h c \bar{\nu} = \frac{h c}{\lambda}$। রিডবার্গ সমীকরণ: $\bar{\nu} = \frac{1}{\lambda} = R_H \left(\frac{1}{n_1^2} - \frac{1}{n_2^2}\right)$ ($n_2 &gt; n_1$)। রিডবার্গ ধ্রুবকের তাত্ত্বিক সমীকরণ: $R_\infty = \frac{m e^4}{8 \epsilon_0^2 c h^3}$। এর সাংখ্যিক মান $R_\infty \approx 1.09737 \times 10^7\text{ m}^{-1}$।</t>
@@ -2219,11 +2119,6 @@
           <t>হাইড্রোজেন পরমাণুর পাঁচটি প্রধান বর্ণালী সিরিজ (Lyman, Balmer, Paschen, Brackett, Pfund)-এর নিম্ন শক্তিস্তর $n_1$ এবং এদের সংশ্লিষ্ট তড়িৎ-চৌম্বকীয় বর্ণালী অঞ্চলগুলো উল্লেখ করো।</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>(১) লাইম্যান সিরিজ ($n_1 = 1, n_2 = 2, 3, \dots$): অতিবেগুনী (Ultraviolet - UV) অঞ্চল। (২) বামার সিরিজ ($n_1 = 2, n_2 = 3, 4, \dots$): দৃশ্যমান (Visible) অঞ্চল (চারটি রেখা $H_\alpha, H_\beta, H_\gamma, H_\delta$ স্পষ্ট দেখা যায়)। (৩) প Paschen সিরিজ ($n_1 = 3, n_2 = 4, 5, \dots$): অবলোহিত (Infrared - IR) অঞ্চল। (৪) ব্র্যাকেট সিরিজ ($n_1 = 4, n_2 = 5, 6, \dots$): দূর অবলোহিত (Far IR) অঞ্চল। (৫) ফান্ড সিরিজ ($n_1 = 5, n_2 = 6, 7, \dots$): দূর অবলোহিত অঞ্চল।</t>
@@ -2269,11 +2164,6 @@
           <t>হাইড্রোজেনের বামার সিরিজের প্রথম রেখা ($H_\alpha$, $n_2 = 3 \to n_1 = 2$)-এর তরঙ্গদৈর্ঘ্য গণনা করো এবং এর দৃশ্যমান বর্ণ কী?</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>সূত্র: $\frac{1}{\lambda} = R_H \left(\frac{1}{2^2} - \frac{1}{3^2}\right) = R_H \left(\frac{1}{4} - \frac{1}{9}\right) = \frac{5}{36} R_H$। অতএব $\lambda = \frac{36}{5 R_H} = \frac{36}{5 \times 1.097 \times 10^7\text{ m}^{-1}} \approx 6.563 \times 10^{-7}\text{ m} = 656.3\text{ nm} = 6563\text{ \AA}$। এই রেখাটি দৃশ্যমান বর্ণালীর লাল (Red) অঞ্চলে অবস্থিত।</t>
@@ -2370,11 +2260,6 @@
           <t>হাইড্রোজেন পরমাণুর একটি নমুনাকে $n = 5$ স্তরে উত্তেজিত করা হলে ইলেকট্রনগুলো ভূমি স্তরে প্রত্যাবর্তনের সময় বর্ণালীতে সর্বোচ্চ কতটি ভিন্ন তরঙ্গদৈর্ঘ্যের বর্ণালী রেখা নির্গত হতে পারে?</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>উচ্চ শক্তিস্তর $n$ থেকে নিম্ন শক্তিস্তরে সংক্রমণের সম্ভাব্য মোট রেখার সংখ্যা কম্বিনেটোরিক্স অনুযায়ী $N = \binom{n}{2} = \frac{n(n-1)}{2}$। এখানে $n = 5$ হলে: $N = \frac{5 \times (5 - 1)}{2} = \frac{5 \times 4}{2} = 10$ টি। এর মধ্যে ৪টি লাইম্যান, ৩টি বামার, ২টি প্যাশেন এবং ১টি ব্র্যাকেট রেখা অন্তর্ভুক্ত থাকে।</t>
@@ -2420,11 +2305,6 @@
           <t>হাইড্রোজেনের বামার সিরিজের দীর্ঘতম তরঙ্গদৈর্ঘ্য ($\lambda_{\max}$) এবং ক্ষুদ্রতম তরঙ্গদৈর্ঘ্যের ($\lambda_{\min}$) অনুপাত কত?</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>বামারের জন্য $n_1 = 2$। দীর্ঘতম তরঙ্গদৈর্ঘ্য ($n_2 = 3$): $\frac{1}{\lambda_{\max}} = R_H \left(\frac{1}{4} - \frac{1}{9}\right) = \frac{5}{36} R_H \Rightarrow \lambda_{\max} = \frac{36}{5 R_H}$। ক্ষুদ্রতম তরঙ্গদৈর্ঘ্য ($n_2 = \infty$): $\frac{1}{\lambda_{\min}} = R_H \left(\frac{1}{4} - \frac{1}{\infty}\right) = \frac{1}{4} R_H \Rightarrow \lambda_{\min} = \frac{4}{R_H}$। অনুপাত: $\frac{\lambda_{\max}}{\lambda_{\min}} = \frac{36 / (5 R_H)}{4 / R_H} = \frac{36}{5 \times 4} = \frac{9}{5} = 1.8$।</t>
@@ -2470,11 +2350,6 @@
           <t>একক আয়নিত হিলিয়াম ($\text{He}^+, Z = 2$)-এর বর্ণালীতে কোন সংক্রমণের তরঙ্গদৈর্ঘ্য হাইড্রোজেনের প্রথম লাইম্যান রেখার ($n = 2 \to 1$) সাথে হুবহু সমান হবে?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>হাইড্রোজেনের লাইম্যান রেখা ($Z = 1$): $\frac{1}{\lambda_H} = R_\infty \left(\frac{1}{1^2} - \frac{1}{2^2}\right) = \frac{3}{4} R_\infty$। $\text{He}^+$ এর জন্য ($Z = 2$): $\frac{1}{\lambda_{\text{He}}} = Z^2 R_\infty \left(\frac{1}{n_1^2} - \frac{1}{n_2^2}\right) = 4 R_\infty \left(\frac{1}{n_1^2} - \frac{1}{n_2^2}\right) = R_\infty \left(\frac{4}{n_1^2} - \frac{4}{n_2^2}\right)$। উভয়কে সমান করতে হলে: $\frac{4}{n_1^2} = 1 \Rightarrow n_1 = 2$, এবং $\frac{4}{n_2^2} = \frac{1}{4} \Rightarrow n_2^2 = 16 \Rightarrow n_2 = 4$। অর্থাৎ $\text{He}^+$-এর $n = 4 \to n = 2$ রূপান্তরের তরঙ্গদৈর্ঘ্য হাইড্রোজেনের $n = 2 \to n = 1$ এর সমান।</t>
@@ -2520,11 +2395,6 @@
           <t>হাইড্রোজেন পরমাণু $n = 2$ স্তর থেকে $n = 1$ স্তরে ফোটন নিঃসরণের সময় পরমাণুটি নিজে সামান্য প্রতিক্ষিপ্ত (Recoil) হয়। এই প্রতিক্ষেপ গতিশক্তি কত এবং এটি ফোটনের শক্তিকে কি উল্লেখযোগ্যভাবে হ্রাস করে?</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>নিঃসৃত ফোটনের শক্তি $E_{\text{ph}} \approx 10.2\text{ eV}$। ফোটনের ভরবেগ $p = \frac{E_{\text{ph}}}{c}$। ভরবেগ সংরক্ষণে পরমাণুর প্রতিক্ষেপ ভরবেগ $p_{\text{atom}} = p$। পরমাণুর রিকয়েল গতিশক্তি $K_R = \frac{p^2}{2 M} = \frac{E_{\text{ph}}^2}{2 M c^2}$। প্রোটনের স্থির শক্তি $M c^2 \approx 938\text{ MeV}$। ফলে $K_R = \frac{(10.2\text{ eV})^2}{2 \times 938 \times 10^6\text{ eV}} \approx \frac{104}{1.88 \times 10^9}\text{ eV} \approx 5.5 \times 10^{-8}\text{ eV}$। এটি $10.2\text{ eV}$-এর তুলনায় এত নগণ্য ($\sim 10^{-9}$ অংশ) যে বর্ণালী রেখার পরিবর্তন সম্পূর্ণ উপেক্ষণীয়।</t>
@@ -2570,11 +2440,6 @@
           <t>১৯১৪ সালে জেমস ফ্রাঙ্ক ও গুস্তাভ হার্টজ (Franck-Hertz) পারদ বাষ্পের মধ্য দিয়ে ইলেকট্রন চালনা করে কীভাবে পরমাণুর বিচ্ছিন্ন শক্তিস্তরের সরাসরি পরীক্ষামূলক প্রমাণ দেন?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>তারা দেখেন যে ত্বরিত ইলেকট্রনের শক্তি $4.9\text{ eV}$-এর কম থাকা পর্যন্ত পারদ পরমাণুর সাথে তাদের স্থিতিস্থাপক সংঘর্ষ হয় এবং কোনো শক্তি ক্ষয় হয় না। কিন্তু বিভব ঠিক $4.9\text{ V}$ বা তার গুণিতকে ($9.8\text{ V}, 14.7\text{ V}$) পৌঁছানো মাত্র ইলেকট্রনগুলো পারদ পরমাণুকে উত্তেজিত করতে সমস্ত গতিশক্তি হারিয়ে ফেলে, ফলে সংগ্রাহক তড়িৎপ্রবাহে তীব্র পতন ঘটে। একই সাথে পারদ বাষ্প থেকে $4.9\text{ eV}$ শক্তির ($\lambda = 253.7\text{ nm}$) অতিবেগুনী ফোটন বিকিরণ হতে দেখা যায়, যা পরমাণুতে বিচ্ছিন্ন কোয়ান্টাম শক্তিস্তরের প্রত্যক্ষ বাস্তব প্রমাণ দেয়।</t>
@@ -2620,11 +2485,6 @@
           <t>বোর পরমাণু মডেলের তিনটি প্রধান ব্যর্থতা বা সীমাবদ্ধতা সংক্ষেপে উল্লেখ করো।</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>(১) বহু-ইলেকট্রন পরমাণুর বর্ণালী: এটি কেবল এক-ইলেকট্রন বিশিষ্ট পরমাণুর (H, $\text{He}^+, \text{Li}^{2+}$) জন্য প্রযোজ্য; বহু-ইলেকট্রন পরমাণুর বর্ণালী ব্যাখ্যা করতে পারে না। (২) সূক্ষ্ম গঠন ও বর্ণালী রেখার তীব্রতা: উচ্চ বিভেদন ক্ষমতার স্পেকট্রোমিটারে দেখা যায় প্রতিটি রেখা আসলে একাধিক নিকটবর্তী সূক্ষ্ম রেখার সমষ্টি (Fine structure), এবং রেখাগুলোর তীব্রতা ভিন্ন ভিন্ন হয় যা বোর মডেল ব্যাখ্যা করতে পারে না। (৩) জেমান প্রভাব ও স্টার্ক প্রভাব: চৌম্বক ক্ষেত্রে বর্ণালী রেখার বিভাজন (Zeeman Effect) এবং তড়িৎ ক্ষেত্রে বিভাজন (Stark Effect) বোর মডেল দিয়ে ব্যাখ্যা করা অসম্ভব।</t>
@@ -2670,11 +2530,6 @@
           <t>১৯১৬ সালে আর্নল্ড সোমারফেল্ড বোর মডেলের সীমাবদ্ধতা দূর করতে কোন দুটি প্রধান সংশোধন অন্তর্ভুক্ত করেন এবং এর মাধ্যমে কোন কোয়ান্টাম সংখ্যার উদ্ভব হয়?</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>সোমারফেল্ড দুটি মৌলিক পরিবর্তন আনেন: (১) বৃত্তাকার কক্ষপথের পরিবর্তে উপবৃত্তাকার (Elliptical) কক্ষপথ প্রস্তাব করেন যার একটি ফোকাসে নিউক্লিয়াস অবস্থান করে, এবং (২) ইলেকট্রনের গতির ওপর আপেক্ষিকীয় ভর বৃদ্ধির প্রভাব ($m = \gamma m_0$) অন্তর্ভুক্ত করেন। উপবৃত্তাকার গতির জন্য দুটি স্বাধীন স্থানাঙ্ক (ব্যাসার্ধীয় $r$ এবং কৌণিক $\theta$) থাকায় প্রধান কোয়ান্টাম সংখ্যা $n$-এর পাশাপাশি 'কক্ষীয় বা অ্যাজিমুথাল কোয়ান্টাম সংখ্যা' ($k$ বা আধুনিক $l$) প্রবর্তিত হয়, যা বর্ণালীর সূক্ষ্ম গঠন ব্যাখ্যা করে।</t>
@@ -2720,11 +2575,6 @@
           <t>এক্স-রে (X-rays) কীভাবে উৎপন্ন হয় এবং আধুনিক কুলিজ নলে (Coolidge tube) ফিলামেন্ট কারেন্ট ও অ্যানোড ভোল্টেজের মাধ্যমে যথাক্রমে এক্স-রের কোন দুটি বৈশিষ্ট্য স্বাধীনভাবে নিয়ন্ত্রণ করা যায়?</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>উচ্চ গতিসম্পন্ন ত্বরিত ইলেকট্রন যখন কোনো ভারী লক্ষ্যবস্তুতে (যেমন টাংস্টেন বা মলিবডেনাম) প্রচণ্ড বেগে আঘাত করে আকস্মিকভাবে থেমে যায়, তখন ইলেকট্রনের গতিশক্তি উচ্চ কম্পাঙ্কের তড়িৎ-চৌম্বকীয় বিকিরণ অর্থাৎ এক্স-রেতে রূপান্তরিত হয়। কুলিজ নলে: (১) ফিলামেন্ট কারেন্ট নিয়ন্ত্রণ করে নির্গত ইলেকট্রনের সংখ্যা বৃদ্ধি করা হয়, যা এক্স-রে রশ্মির তীব্রতা (Intensity) নিয়ন্ত্রণ করে। (২) অ্যানোড বিভব ($V$) বৃদ্ধি করে ইলেকট্রনের বেগ ও শক্তি বাড়ানো হয়, যা এক্স-রের সর্বোচ্চ কম্পাঙ্ক ও ভেদন ক্ষমতা বা তীক্ষ্ণতা (Penetrating power বা Quality) নিয়ন্ত্রণ করে।</t>
@@ -2770,11 +2620,6 @@
           <t>অবিচ্ছিন্ন এক্স-রে (Continuous X-rays বা Bremsstrahlung) সৃষ্টির ভৌত কারণ কী এবং ন্যূনতম তরঙ্গদৈর্ঘ্যের জন্য ডুয়ান-হান্ট (Duane-Hunt Law) সমীকরণটি লেখো।</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>লক্ষ্যবস্তুর নিউক্লিয়াসের শক্তিশালী তড়িৎক্ষেত্রের প্রভাবে দ্রুতগামী ইলেকট্রন যখন মন্থরিত বা দিক পরিবর্তন করে, তখন ক্লাসিক্যাল ও কোয়ান্টাম বিকিরণ নীতিতে ইলেকট্রন তার গতিশক্তি সরাসরি ফোটন আকারে বিকিরণ করে; একে ব্রেকিং রেডিয়েশন (Bremsstrahlung) বলে। যদি একটি ইলেকট্রন একটিমাত্র সংঘর্ষেই তার সম্পূর্ণ গতিশক্তি $eV$ একটিমাত্র ফোটনে রূপান্তর করে, তবে ফোটনটির শক্তি সর্বোচ্চ এবং তরঙ্গদৈর্ঘ্য সর্বনিম্ন হয়: $h\nu_{\max} = \frac{hc}{\lambda_{\min}} = eV$। ডুয়ান-হান্ট সমীকরণ: $\lambda_{\min} = \frac{hc}{eV} = \frac{12400}{V}\text{ \AA}$ (যেখানে $V$ ভোল্ট এককে)।</t>
@@ -2820,11 +2665,6 @@
           <t>বৈশিষ্ট্যমূলক এক্স-রে কীভাবে উৎপন্ন হয় এবং $K_\alpha$ ও $K_\beta$ রেখার মধ্যে শক্তির পার্থক্য ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>যখন আপতিত উচ্চ শক্তির ইলেকট্রন লক্ষ্যবস্তুর পরমাণুর ভেতরের সবচেয়ে গভীর কক্ষপথের (যেমন $K$-শেল) একটি ইলেকট্রনকে আঘাত করে সম্পূর্ণ বের করে দেয়, তখন $K$-শেলে একটি শূন্যস্থান সৃষ্টি হয়। এই শূন্যস্থান পূরণের জন্য বাইরের শক্তিস্তর থেকে ইলেকট্রন লাফিয়ে পড়ে। $L$-শেল ($n = 2$) থেকে $K$-শেলে ($n = 1$) ইলেকট্রন নামলে নির্গত হয় $K_\alpha$ এক্স-রে। আর $M$-শেল ($n = 3$) থেকে $K$-শেলে নামলে নির্গত হয় উচ্চতর শক্তির $K_\beta$ এক্স-রে ($E_{K_\beta} &gt; E_{K_\alpha}$, ফলে $\lambda_{K_\beta} &lt; \lambda_{K_\alpha}$)।</t>
@@ -2870,11 +2710,6 @@
           <t>১৯১৩ সালে হেনরি মোজলে আবিষ্কৃত মোজলের সূত্রটি লেখো এবং এটি পর্যায় সারণির মৌলিক ভিত্তি পুনর্গঠনে কী ঐতিহাসিক অবদান রেখেছিল?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>মোজলের সূত্রানুযায়ী বৈশিষ্ট্যমূলক এক্স-রের নির্দিষ্ট বর্ণালী রেখার কম্পাঙ্কের বর্গমূল লক্ষ্যবস্তুর পারমাণবিক সংখ্যা $Z$-এর সমানুপাতিক: $\sqrt{\nu} = a(Z - b)$, যেখানে $a$ ও $b$ হলো ধ্রুবক ($K_\alpha$ রেখার জন্য স্ক্রিনিং ধ্রুবক $b \approx 1$)। মোজলে প্রমাণ করেন যে মৌলের মৌলিক রাসায়নিক ও ভৌত ধর্ম পারমাণবিক ভরের (Atomic weight) ওপর নয়, বরং পারমাণবিক সংখ্যা (Atomic number - প্রোটন সংখ্যা $Z$)-এর ওপর নির্ভরশীল। ফলে মেন্ডেলিফের পর্যায় সারণিকে পারমাণবিক সংখ্যার ভিত্তিতে পুনর্গঠন করা হয়।</t>
@@ -2920,11 +2755,6 @@
           <t>মোজলের সূত্রে $K_\alpha$ বিকিরণের ক্ষেত্রে স্ক্রিনিং ধ্রুবক $b = 1$ ধরা হয় কেন এবং $L_\alpha$ বিকিরণে এর মান কত হয়?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>$K$-শেলে ইলেকট্রন পতনের পূর্বে সেখানে অন্য আরেকটি অবশিষ্ট ইলেকট্রন নিউক্লিয়াসের আধানকে আংশিক ঢেকে রাখে বা স্ক্রিন করে। ফলে $L$-শেল থেকে পতিত ইলেকট্রনটি কার্যকর আধান অনুভব করে $Z_{\text{eff}} = Z - 1$, তাই $K_\alpha$-এর জন্য $b = 1$। $L$-শেলের শূন্যস্থান পূরণের সময় ($L_\alpha$ রেখা) ভেতরের $K$-শেলের ২টি ইলেকট্রন এবং $L$-শেলের অন্যান্য ইলেকট্রন মিলে অধিক কার্যকর আবরণ সৃষ্টি করে, ফলে $L_\alpha$-এর ক্ষেত্রে স্ক্রিনিং ধ্রুবক $b \approx 7.4$ হয়।</t>
@@ -2970,11 +2800,6 @@
           <t>স্ফটিকের সমান্তরাল পারমাণবিক তলের ব্যবধান $d$ হলে এক্স-রে অপবর্তনের জন্য ব্র্যাগের সূত্রটি (Bragg's Law) প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>সমান্তরাল তলগুলোর মধ্যকার ব্যবধান $d$ এবং তলের সাথে আপতিত রশ্মির কোণ (গ্ল্যান্সিং কোণ বা Bragg angle) $\theta$। দুটি পাশাপাশি তলের পরমাণু থেকে প্রতিফলিত রশ্মিদ্বয়ের মধ্যকার জ্যামিতিক পথ পার্থক্য হলো $\Delta x = 2 d \sin\theta$। গঠনমূলক ব্যতিচারের শর্তানুযায়ী পথ পার্থক্য তরঙ্গদৈর্ঘ্যের পূর্ণ গুণিতক হতে হবে: $2 d \sin\theta = n \lambda$ ($n = 1, 2, 3, \dots$)। এটিই ব্র্যাগের সূত্র।</t>
@@ -3020,11 +2845,6 @@
           <t>একটি ধাতুর $K_\alpha$ রেখার তরঙ্গদৈর্ঘ্য $0.180\text{ nm}$ এবং অপর একটি পরিচিত ধাতু যার $Z_1 = 30$ তার $K_\alpha$ তরঙ্গদৈর্ঘ্য $0.154\text{ nm}$ হলে অজানা ধাতুটির পারমাণবিক সংখ্যা $Z_2$ কত?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>মোজলের সূত্রানুযায়ী $\nu \propto (Z - 1)^2 \Rightarrow \frac{1}{\lambda} \propto (Z - 1)^2 \Rightarrow \frac{\lambda_1}{\lambda_2} = \frac{(Z_2 - 1)^2}{(Z_1 - 1)^2}$। মান বসিয়ে: $\frac{0.154}{0.180} = \frac{(Z_2 - 1)^2}{(30 - 1)^2} = \frac{(Z_2 - 1)^2}{29^2} \Rightarrow (Z_2 - 1)^2 = 841 \times \frac{0.154}{0.180} \approx 841 \times 0.8556 \approx 719.5$। বর্গমূল করলে: $Z_2 - 1 = \sqrt{719.5} \approx 26.82 \approx 27 \Rightarrow Z_2 \approx 28$ (নিকেল)।</t>
@@ -3070,11 +2890,6 @@
           <t>চিকিৎসাবিজ্ঞান ও পদার্থবিজ্ঞানে 'কঠোর এক্স-রে' (Hard X-rays) এবং 'কোমল এক্স-রে' (Soft X-rays)-এর মধ্যে তরঙ্গদৈর্ঘ্য ও ভেদন ক্ষমতার মূল পার্থক্য কী?</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>কঠোর এক্স-রে (Hard X-rays) অতি উচ্চ ভোল্টেজে উৎপন্ন হয়; এদের তরঙ্গদৈর্ঘ্য অত্যন্ত ক্ষুদ্র ($\lambda \sim 0.01 - 0.1\text{ nm}$), কম্পাঙ্ক ও ফোটন শক্তি অতি উচ্চ এবং এদের ভেদন ক্ষমতা (Penetrating power) অত্যন্ত প্রবল, যা হাড়ের ফ্র্যাকচার বা মেটাল ওয়েল্ডিং পরীক্ষায় ব্যবহৃত হয়। কোমল এক্স-রে (Soft X-rays) অপেক্ষাকৃত কম ভোল্টেজে তৈরি হয়; এদের তরঙ্গদৈর্ঘ্য তুলনামূলক দীর্ঘ ($\lambda \sim 0.1 - 10\text{ nm}$), শক্তি কম এবং ভেদন ক্ষমতা দুর্বল, যা প্রধানত ত্বক বা নরম টিস্যু পর্যবেক্ষণে ব্যবহৃত হয়।</t>
@@ -3120,11 +2935,6 @@
           <t>একটি এক্স-রে টিউব $50\text{ kV}$ বিভবে এবং $20\text{ mA}$ কারেন্টে চালিত হচ্ছে। টিউবের কার্যদক্ষতা মাত্র $1\%$ হলে প্রতি সেকেন্ডে অ্যানোড টার্গেটে কত জুল তাপ উৎপন্ন হয়?</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>মোট বৈদ্যুতিক ক্ষমতা $P = V I = (50 \times 10^3\text{ V}) \times (20 \times 10^{-3}\text{ A}) = 1000\text{ W} = 1000\text{ J/s}$। যেহেতু দক্ষতা মাত্র $1\%$, তাই মাত্র $1\%$ শক্তি এক্স-রে হিসেবে নির্গত হয় এবং অবশিষ্ট $99\%$ শক্তি অ্যানোডে মারাত্মক তাপে রূপান্তরিত হয়। প্রতি সেকেন্ডে উৎপন্ন তাপীয় শক্তি $P_{\text{heat}} = 0.99 \times 1000\text{ W} = 990\text{ J/s} = 990\text{ W}$। এজন্য অ্যানোডকে পানি বা তেল দিয়ে অনবরত ঠান্ডা রাখতে হয়।</t>
@@ -3170,11 +2980,6 @@
           <t>ভর সংখ্যা $A$ বিশিষ্ট কোনো নিউক্লিয়াসের ব্যাসার্ধ $R$-এর গবেষণালব্ধ সমীকরণটি লেখো এবং $R_0$-এর মান কত? এর থেকে প্রমাণ করো যে নিউক্লিয়াসের আয়তন ভর সংখ্যার সমানুপাতিক।</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>ইলেকট্রন ও নিউট্রন বিক্ষেপণ পরীক্ষা থেকে প্রাপ্ত সমীকরণ: $R = R_0 A^{1/3}$ যেখানে $R_0 \approx 1.2\text{ fm} = 1.2 \times 10^{-15}\text{ m}$। নিউক্লিয়াসকে গোলক বিবেচনা করলে এর আয়তন $V = \frac{4}{3}\pi R^3 = \frac{4}{3}\pi (R_0 A^{1/3})^3 = \left(\frac{4}{3}\pi R_0^3\right) A$। যেহেতু ব্র্যাকেটের অংশটি একটি ধ্রুবক, সুতরাং $V \propto A$। অর্থাৎ নিউক্লিয়াসের আয়তন তার মোট নিউক্লিয়ন সংখ্যার সরাসরি সমানুপাতিক।</t>
@@ -3220,11 +3025,6 @@
           <t>নিউক্লীয় ঘনত্ব $\rho$ ভর সংখ্যা $A$-এর ওপর নির্ভর করে না কেন? নিউক্লীয় ঘনত্বের গড় সাংখ্যিক মান নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>প্রতিটি নিউক্লিয়নের গড় ভর $m_n \approx 1.66 \times 10^{-27}\text{ kg}$। ভর সংখ্যা $A$ হলে মোট ভর $M = A m_n$। আয়তন $V = \frac{4}{3}\pi R^3 = \frac{4}{3}\pi R_0^3 A$। নিউক্লীয় ঘনত্ব $\rho = \frac{M}{V} = \frac{A m_n}{\frac{4}{3}\pi R_0^3 A} = \frac{3 m_n}{4\pi R_0^3}$। সমীকরণে লব ও হর উভয় থেকে $A$ বাতিল হয়ে যাওয়ায় ঘনত্ব সকল নিউক্লিয়াসের জন্য সম্পূর্ণ ধ্রুবক। মান: $\rho \approx \frac{3 \times 1.66 \times 10^{-27}}{4\pi \times (1.2 \times 10^{-15})^3} \approx 2.3 \times 10^{17}\text{ kg/m}^3$। এটি পানির ঘনত্বের চেয়ে প্রায় $10^{14}$ গুণ বেশি।</t>
@@ -3270,11 +3070,6 @@
           <t>নিউক্লিয়ার পদার্থবিজ্ঞানে আইসোটোপ (Isotopes), আইসোবার (Isobars), আইসোটোন (Isotones) এবং আইসোমার (Isomers)-এর সুনির্দিষ্ট সংজ্ঞা ও প্রতিটির একটি করে উদাহরণ দাও।</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>(১) আইসোটোপ: একই প্রোটন সংখ্যা ($Z$), কিন্তু ভিন্ন ভর সংখ্যা ($A$) (উদা. $_{6}^{12}\text{C}, _{6}^{14}\text{C}$)। (২) আইসোবার: একই ভর সংখ্যা ($A$), কিন্তু ভিন্ন প্রোটন সংখ্যা ($Z$) (উদা. $_{6}^{14}\text{C}, _{7}^{14}\text{N}$)। (৩) আইসোটোন: একই নিউট্রন সংখ্যা ($N = A - Z$), কিন্তু ভিন্ন প্রোটন সংখ্যা (উদা. $_{6}^{14}\text{C}$ ও $_{8}^{16}\text{O}$, উভয়েই $N = 8$)। (৪) আইসোমার: একই $Z$ এবং একই $A$, কিন্তু ভিন্ন অভ্যন্তরীণ কোয়ান্টাম নিউক্লীয় শক্তিস্তর ও জীবনকাল (উদা. $^{99m}\text{Tc}$ ও $^{99}\text{Tc}$)।</t>
@@ -3320,11 +3115,6 @@
           <t>প্রকৃতির চারটি মৌলিক বলের মধ্যে তীব্র নিউক্লীয় বলের (Strong Nuclear Force) প্রধান তিনটি অনন্য বৈশিষ্ট্য উল্লেখ করো।</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>(১) সর্বাধিক তীব্রতা ও স্বল্প পাল্লা: এটি মহাবিশ্বের সবচেয়ে শক্তিশালী বল (মহাকর্ষ বল অপেক্ষা প্রায় $10^{38}$ গুণ শক্তিশালী), তবে এর পাল্লা অত্যন্ত সীমিত বা স্বল্প ($\sim 1-2\text{ fm}$)। দূরত্বের বাইরে এটি দ্রুত শূন্যে নেমে আসে। (২) আধান নিরপেক্ষতা (Charge Independence): নিউট্রন-নিউট্রন ($n-n$), প্রোটন-প্রোটন ($p-p$) এবং নিউট্রন-প্রোটন ($n-p$) এর মধ্যে নিউক্লীয় বল হুবহু সমান শক্তির হয়। (৩) সম্পৃক্ততা ও অতি-স্বল্প দূরত্বে বিকর্ষণ: এটি সম্পৃক্ত বল (প্রতিটি নিউক্লিয়ন কেবল নিকটবর্তী প্রতিবেশীকে আকর্ষণ করে) এবং দূরত্ব $0.5\text{ fm}$-এর কম হলে এটি প্রচণ্ড বিকর্ষণমূলক বলে পরিণত হয় যা নিউক্লিয়াসকে নিজের ভেতর ভেঙে পড়তে দেয় না।</t>
@@ -3370,11 +3160,6 @@
           <t>১৯৩৫ সালে হিদেকি ইউকাওয়া (Hideki Yukawa) নিউক্লীয় বলের উৎপত্তির ব্যাখ্যায় কোন কণার বিনিময় তত্ত্ব দেন এবং মেসনের আনুমানিক ভর কীভাবে তিনি অনুমান করেছিলেন?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>ইউকাওয়া প্রস্তাব করেন যে তড়িৎ-চৌম্বকীয় বল যেমন ফোটন বিনিময়ের মাধ্যমে ঘটে, তেমনি নিউক্লিয়নগুলোর মধ্যে তীব্র আকর্ষণ বল অবিরাম পাই-মেসন ($\pi$-meson বা Pion) কণার বিনিময়ের মাধ্যমে ঘটে। শক্তি-সময় অনিশ্চয়তা নীতি ($\Delta E \Delta t \approx \hbar$) প্রয়োগ করে তিনি দেখান যে নিউক্লীয় পাল্লা $R \approx c \Delta t \approx \frac{\hbar c}{m_\pi c^2} \Rightarrow m_\pi \approx \frac{\hbar}{R c}$। $R \approx 1.5\text{ fm}$ বসালে মেসনের ভর পাওয়া যায় প্রায় $200-300 m_e$ (ইলেকট্রনের ভরের প্রায় ২৭০ গুণ)। পরবর্তীতে ১৯৪৭ সালে পাওয়েল বাস্তবে পাইয়ন আবিষ্কার করেন।</t>
@@ -3420,11 +3205,6 @@
           <t>লোহার নিউক্লিয়াসের ($_{26}^{56}\text{Fe}$) পারমাণবিক ভর সংখ্যা $A = 56$ হলে এর নিউক্লীয় ব্যাসার্ধ এবং আয়তন কত? ($R_0 = 1.2\text{ fm}$)</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>ব্যাসার্ধ: $R = R_0 A^{1/3} = 1.2 \times (56)^{1/3}\text{ fm}$। যেহেতু $56^{1/3} \approx 3.826$, সুতরাং $R = 1.2 \times 3.826\text{ fm} \approx 4.59\text{ fm} = 4.59 \times 10^{-15}\text{ m}$। আয়তন: $V = \frac{4}{3}\pi R^3 = \frac{4}{3}\pi (4.59 \times 10^{-15}\text{ m})^3 \approx \frac{4}{3}\pi \times 96.7 \times 10^{-45}\text{ m}^3 \approx 4.05 \times 10^{-43}\text{ m}^3$।</t>
@@ -3470,11 +3250,6 @@
           <t>পারমাণবিক ভর একক ($1\text{ u}$ বা $1\text{ amu}$)-এর আধুনিক আন্তর্জাতিক সংজ্ঞা কী এবং এর সমতুল্য শক্তি মেগা-ইলেকট্রন ভোল্টে ($\text{MeV}$) কত?</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>আধুনিক সংজ্ঞানুযায়ী একটি অনুত্তেজিত কার্বন-১২ ($_{6}^{12}\text{C}$) পরমাণুর ভরের ঠিক $\frac{1}{12}$ অংশকে $1\text{ u}$ (বা $1\text{ amu}$) বলা হয়। ভর মান: $1\text{ u} = \frac{12 \times 10^{-3}\text{ kg}}{12 \times 6.022 \times 10^{23}} \approx 1.66054 \times 10^{-27}\text{ kg}$। আইনস্টাইনের সমীকরণ $E = m c^2$ অনুযায়ী এর সমতুল্য শক্তি: $E = \frac{1.66054 \times 10^{-27} \times (2.998 \times 10^8)^2}{1.602 \times 10^{-13}}\text{ MeV} \approx 931.5\text{ MeV}$।</t>
@@ -3520,11 +3295,6 @@
           <t>হালকা স্থিতিশীল নিউক্লিয়াসে $N/Z \approx 1$ হলেও ভারী স্থিতিশীল নিউক্লিয়াসের ক্ষেত্রে (যেমন সীসা $_{82}^{208}\text{Pb}$) এই অনুপাত বৃদ্ধি পেয়ে প্রায় $1.5$-এ পৌঁছায় কেন?</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>হালকা নিউক্লিয়াসে প্রোটনের সংখ্যা কম থাকায় তাদের মধ্যকার কুলম্ব বিকর্ষণ বল দুর্বল থাকে, ফলে সমান সংখ্যক প্রোটন ও নিউট্রন ($N \approx Z$) সর্বাধিক বন্ধন স্থায়িত্ব দেয়। কিন্তু পারমাণবিক সংখ্যা $Z$ বৃদ্ধি পেলে প্রোটনগুলোর পারস্পরিক কুলম্বীয় বিকর্ষণ বল দীর্ঘ-পাল্লার হওয়ায় $Z^2$ হারে দ্রুত বৃদ্ধি পায়। বিপরীতে তীব্র নিউক্লীয় বল স্বল্প-পাল্লার হওয়ায় কেবল নিকটবর্তী কণার মধ্যে সীমাবদ্ধ থাকে। এই ক্রমবর্ধমান কুলম্ব বিকর্ষণকে প্রশমিত করে নিউক্লিয়াসকে স্থিতিশীল রাখতে অতিরিক্ত নিউট্রনের প্রয়োজন হয়, ফলে ভারী মৌলে $N/Z$ বৃদ্ধি পেয়ে প্রায় ১.৫-এ পৌঁছায়।</t>
@@ -3570,11 +3340,6 @@
           <t>নিউক্লিয়ার পদার্থবিজ্ঞানে ম্যাজিক সংখ্যাগুলো ($2, 8, 20, 28, 50, 82, 126$) বলতে কী বোঝায় এবং এই সংখ্যাবিশিষ্ট নিউক্লিয়াসগুলো কেন অস্বাভাবিক স্থিতিশীল হয়?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>পরমাণুতে যেমন ইলেকট্রন শেল পূর্ণ হলে নিষ্ক্রিয় গ্যাসগুলো (২, ১০, ১৮...) রাসায়নিকভাবে অতি স্থিতিশীল হয়, তেমনি নিউক্লিয়াসের অভ্যন্তরে প্রোটন ও নিউট্রনদের নিজস্ব কোয়ান্টাম শক্তিস্তর বা শেল (Nuclear Shell Model) থাকে। যখন নিউক্লিয়াসে প্রোটন সংখ্যা বা নিউট্রন সংখ্যা $2, 8, 20, 28, 50, 82, 126$ হয়, তখন নিউক্লিয়ার শেলগুলো সম্পূর্ণ পূর্ণ হয়। এই সংখ্যাগুলোকে ম্যাজিক সংখ্যা বলে। যেমন $_{82}^{208}\text{Pb}$ দ্বৈত-ম্যাজিক নিউক্লিয়াস ($Z = 82, N = 126$) হওয়ায় এটি অত্যন্ত স্থিতিশীল।</t>
@@ -3620,11 +3385,6 @@
           <t>কোন ধরনের নিউক্লিয়াসের মোট নিউক্লিয়ার স্পিন শূন্য ($I = 0$) হয় এবং চৌম্বকীয় অনুরণন ইমেজিং (MRI) প্রযুক্তিতে মানবদেহে প্রধানত কোন নিউক্লিয়াসটি ব্যবহৃত হয় ও কেন?</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>যেসব নিউক্লিয়াসে প্রোটন সংখ্যা এবং নিউট্রন সংখ্যা উভয়ই জোড় (Even-Even nuclei, যেমন $_{6}^{12}\text{C}, _{8}^{16}\text{O}$), তাদের প্রোটন ও নিউট্রনগুলো জোড়ায় জোড়ায় বিপরীত স্পিনে আবদ্ধ হয়ে নিট স্পিন শূন্য করে ফেলে ($I = 0$), ফলে এদের কোনো চৌম্বক ভ্রামক থাকে না। বিজোড় সংখ্যক নিউক্লিয়ন বিশিষ্ট নিউক্লিয়াসে অশূন্য স্পিন ($I \neq 0$) থাকে। মানবদেহের প্রায় ৭০% পানি হওয়ায় প্রচুর হাইড্রোজেন নিউক্লিয়াস (একক প্রোটন, যার স্পিন $I = 1/2$ ও প্রবল চৌম্বক ভ্রামক রয়েছে) বিদ্যমান; এজন্য এমআরআই (MRI) প্রযুক্তিতে হাইড্রোজেন প্রোটনের নিউক্লিয়ার চৌম্বক অনুরণন ব্যবহার করা হয়।</t>
@@ -3654,7 +3414,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>বোর পরমাণু মডেল ও কক্ষপথের শক্তি (সমস্যা 1)</t>
+          <t>বোর পরমাণু মডেল ও হাইড্রোজেন বর্ণালী (Bohr Model &amp; Spectra)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3663,35 +3423,29 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:bohr-atom[size:medium]##
-[সমস্যা 1: বোর পরমাণু মডেল ও কক্ষপথের শক্তি]
-##PRESET:bohr-atom[size:medium]##
-হাইড্রোজেন পরমাণুর ভূমিস্তরের শক্তি $E_1 = -13.6\text{ eV}$। বোরের স্বীকার্যানুসারে 4-তম কক্ষপথের শক্তি ($E_n = E_1/n^2$) এবং কক্ষপথের ব্যাসার্ধ ($r_n = n^2 r_1$) কত? ($r_1 = 0.53\text{ \AA}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+বোর পরমাণু মডেল অনুসারে হাইড্রোজেন পরমাণুর ১ম বোর কক্ষপথের ব্যাসার্ধ $r_1 = 0.529\text{ Å}$। (ক) ৩য় কক্ষপথের ($n = 3$) ব্যাসার্ধ $r_3$, (খ) ১ম ও ৩য় কক্ষপথে ইলেকট্রনের কক্ষীয় দ্রুতি $v_1$ ও $v_3$, এবং (গ) ৩য় কক্ষপথে মোট শক্তি $E_3$ নির্ণয় কর। ($E_1 = -13.6\text{ eV}$)।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:bohr-atom[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 1)।</t>
+          <t>(ক) বোর ব্যাসার্ধ $r_n = n^2 r_1 \implies r_3 = 3^2(0.529\text{ Å}) = 9 \times 0.529 = 4.761\text{ Å} = 0.4761\text{ nm}$। (খ) দ্রুতি $v_n = \frac{v_1}{n}$। $v_1 = \frac{e^2}{2\epsilon_0 h} \approx 2.187 \times 10^6\text{ m/s}$। $v_3 = \frac{v_1}{3} = \frac{2.187 \times 10^6}{3} = 7.29 \times 10^5\text{ m/s}$। (গ) শক্তি $E_n = \frac{E_1}{n^2} \implies E_3 = \frac{-13.6\text{ eV}}{9} \approx -1.511\text{ eV}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(ক) $r_3 = 4.761\text{ Å}$, (খ) $v_1 = 2.187 \times 10^6\text{ m/s}, v_3 = 7.29 \times 10^5\text{ m/s}$, (গ) $E_3 = -1.511\text{ eV}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3711,12 +3465,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় ক্ষয় ধ্রুবক ও অর্ধায়ু (সমস্যা 2)</t>
+          <t>বোর পরমাণু মডেল ও হাইড্রোজেন বর্ণালী (Bohr Model &amp; Spectra)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3724,31 +3478,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>##PRESET:decay-curve[size:medium]##
-[সমস্যা 2: তেজস্ক্রিয় ক্ষয় ধ্রুবক ও অর্ধায়ু]
-##PRESET:decay-curve[size:medium]##
-একটি তেজস্ক্রিয় আইসোটোপের অর্ধায়ু $T_{1/2} = 5.0\text{ দিন}$। মৌলটির ক্ষয় ধ্রুবক ($\lambda$) কত এবং কত দিন পর প্রাথমিক তেজস্ক্রিয় পরমাণুর মাত্র $6.25\%$ অবশিষ্ট থাকবে?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+হাইড্রোজেন পরমাণুর বামার সিরিজের (Balmer series, $n_1 = 2$) দীর্ঘতম তরঙ্গদৈর্ঘ্য ($H_lpha$ রেখা) এবং ক্ষুদ্রতম তরঙ্গদৈর্ঘ্যের (সিরিজ সীমা) মান নির্ণয় কর। ($R_H = 1.097 \times 10^7\text{ m}^{-1}$)।</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##PRESET:decay-curve[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 2)।</t>
+          <t>রিডবার্গ সমীকরণ: $\frac{1}{\lambda} = R_H\left(\frac{1}{n_1^2} - \frac{1}{n_2^2}\right)$। বামারের ক্ষেত্রে $n_1 = 2$। দীর্ঘতম তরঙ্গদৈর্ঘ্যে $n_2 = 3$: $\frac{1}{\lambda_{\max}} = R_H\left(\frac{1}{4} - \frac{1}{9}\right) = \frac{5}{36}R_H \implies \lambda_{\max} = \frac{36}{5 R_H} = \frac{36}{5(1.097 \times 10^7)} = \frac{36}{5.485 \times 10^7} \approx 6.563 \times 10^{-7}\text{ m} = 656.3\text{ nm}$। সিরিজ সীমায় ($n_2 \to \infty$): $\frac{1}{\lambda_{\min}} = \frac{R_H}{4} \implies \lambda_{\min} = \frac{4}{R_H} = \frac{4}{1.097 \times 10^7} \approx 3.646 \times 10^{-7}\text{ m} = 364.6\text{ nm}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>দীর্ঘতম তরঙ্গদৈর্ঘ্য $\lambda_{\max} = 656.3\text{ nm} = 6563\text{ Å}$, ক্ষুদ্রতম তরঙ্গদৈর্ঘ্য $\lambda_{\min} = 364.6\text{ nm} = 3646\text{ Å}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3768,7 +3516,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>হাইড্রোজেন বর্ণালীর বামার ও লাইম্যান সিরিজ (সমস্যা 3)</t>
+          <t>বোর পরমাণু মডেল ও হাইড্রোজেন বর্ণালী (Bohr Model &amp; Spectra)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3777,29 +3525,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: হাইড্রোজেন বর্ণালীর বামার ও লাইম্যান সিরিজ]
-হাইড্রোজেনের একটি ইলেকট্রন $n = 6$ শক্তিস্তর হতে $n = 2$ স্তরে লাফ দিলে নির্গত ফোটনের তরঙ্গদৈর্ঘ্য কত হবে? (রিডবার্গ ধ্রুবক $R_H = 1.097 \times 10^7\text{ m}^{-1}$)</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+লাইম্যান সিরিজের (Lyman series, $n_1 = 1$) সিরিজ সীমার তরঙ্গদৈর্ঘ্য $\lambda_{	ext{limit}}$ কত? এই ফোটনটির শক্তি কত ইলেকট্রন ভোল্ট?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 3)।</t>
+          <t>$n_1 = 1, n_2 \to \infty$: $\frac{1}{\lambda} = R_H\left(\frac{1}{1^2} - 0\right) = R_H \implies \lambda = \frac{1}{R_H} = \frac{1}{1.097 \times 10^7\text{ m}^{-1}} \approx 9.1158 \times 10^{-8}\text{ m} = 91.16\text{ nm}$। শক্তি $E = \frac{h c}{\lambda} = \frac{1240\text{ eV}\cdot\text{nm}}{91.16\text{ nm}} = 13.60\text{ eV}$ (এটি হাইড্রোজেন পরমাণুর আয়নীকরণ বিভবের সমান)।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>তরঙ্গদৈর্ঘ্য $\lambda = 91.16\text{ nm} = 911.6\text{ Å}$, ফোটন শক্তি $E = 13.60\text{ eV}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3819,12 +3567,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>নিউক্লিয়াসের বন্ধন শক্তি ও ভর ত্রুটি (সমস্যা 4)</t>
+          <t>বোর পরমাণু মডেল ও হাইড্রোজেন বর্ণালী (Bohr Model &amp; Spectra)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3832,25 +3580,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[সমস্যা 4: নিউক্লিয়াসের বন্ধন শক্তি ও ভর ত্রুটি]
-একটি হিলিয়াম নিউক্লিয়াসের (${}_2^4\text{He}$) ভর $4.0015\text{ u}$। দুটি প্রোটন ও দুটি নিউট্রনের মোট ভর $4.0319\text{ u}$ হলে ভর ত্রুটি এবং প্রতি নিউক্লিয়ন বন্ধন শক্তি কত মেগা-ইলেকট্রন ভোল্ট (MeV)? ($1\text{ u} = 931.5\text{ MeV}$)</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একক আয়নিত হিলিয়াম পরমাণুর ($	ext{He}^+, Z = 2$) ১ম বোর কক্ষপথের ব্যাসার্ধ $r_1$ এবং ১ম কক্ষপথের শক্তি $E_1$ কত?</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 4)।</t>
+          <t>হাইড্রোজেন সদৃশ আয়নে: $r_n = \frac{n^2}{Z} r_1(H) = \frac{1}{2}(0.529\text{ Å}) = 0.2645\text{ Å}$। শক্তি $E_n = -13.6 \frac{Z^2}{n^2}\text{ eV} \implies E_1 = -13.6 \times \frac{2^2}{1^2} = -13.6 \times 4 = -54.40\text{ eV}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>ব্যাসার্ধ $r_1(\text{He}^+) = 0.2645\text{ Å}$, শক্তি $E_1(\text{He}^+) = -54.40\text{ eV}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3870,7 +3618,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় নমুনার সক্রিয়তা (Activity) (সমস্যা 5)</t>
+          <t>বোর পরমাণু মডেল ও হাইড্রোজেন বর্ণালী (Bohr Model &amp; Spectra)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3879,29 +3627,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: তেজস্ক্রিয় নমুনার সক্রিয়তা (Activity)]
-একটি তেজস্ক্রিয় নমুনার ক্ষয় ধ্রুবক $\lambda = 0.03\text{ s}^{-1}$ এবং এতে উপস্থিত অবিঘটিত পরমাণুর সংখ্যা $N = 4 \times 10^{18}$। নমুনাটির বর্তমান সক্রিয়তা কত কুরি (Curie)? ($1\text{ Ci} = 3.7 \times 10^{10}\text{ Bq}$)</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি হাইড্রোজেন পরমাণু $n = 1$ ভূমি অবস্থা হতে $n = 4$ অবস্থায় উত্তেজিত হলো। পরমাণুটি পুনরায় নিম্ন শক্তি স্তরে প্রত্যাবর্তনের সময় বর্ণালীতে সর্বোচ্চ কতটি ভিন্ন ভিন্ন তরঙ্গদৈর্ঘ্যের রেখা নির্গত হতে পারে?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 5)।</t>
+          <t>বর্ণালী রেখা সংখ্যা $N = \frac{n(n - 1)}{2}$। $n = 4$ হলে: $N = \frac{4(4 - 1)}{2} = \frac{4 \times 3}{2} = 6$ টি রেখা (লাইম্যানের ৩টি: $4\to 1, 3\to 1, 2\to 1$; বামারের ২টি: $4\to 2, 3\to 2$; প্যাশেনের ১টি: $4\to 3$)।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>সর্বোচ্চ নির্গত বর্ণালী রেখা সংখ্যা $N = 6$ টি</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3921,12 +3669,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় গড় আয়ু ও অর্ধায়ু সম্পর্ক (সমস্যা 6)</t>
+          <t>বোর পরমাণু মডেল ও হাইড্রোজেন বর্ণালী (Bohr Model &amp; Spectra)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3934,25 +3682,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: তেজস্ক্রিয় গড় আয়ু ও অর্ধায়ু সম্পর্ক]
-একটি তেজস্ক্রিয় রেডিয়াম নমুনার গড় আয়ু $\tau = 400\text{ বছর}$। এর অর্ধায়ু ($T_{1/2} = 0.693\tau$) কত বছর হবে?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+বোর স্বীকার্য অনুসারে ১ম বোর কক্ষপথে ঘূর্ণায়মান ইলেকট্রনের কক্ষপথের পরিধি ($2\pi r_1$) ইলেকট্রনের দ্য ব্রয় তরঙ্গদৈর্ঘ্যের ($\lambda_1$) সমান—তা প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 6)।</t>
+          <t>বোরের ২য় স্বীকার্য: কৌণিক ভরবেগ $m v r = \frac{n h}{2\pi} \implies 2\pi r = \frac{n h}{m v}$। দ্য ব্রয়ের সমীকরণ অনুসারে ইলেকট্রনের তরঙ্গদৈর্ঘ্য $\lambda = \frac{h}{m v}$। অতএব $2\pi r = n \lambda$। $n = 1$-এর জন্য $2\pi r_1 = \lambda_1$। অর্থাৎ বোর কক্ষপথ হলো ইলেকট্রন তরঙ্গের একটি পূর্ণাঙ্গ স্থির তরঙ্গ লুপ।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>$2\pi r_n = n \lambda$ ($n=1$-এর জন্য $2\pi r_1 = \lambda_1$)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3972,7 +3720,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>নিউক্লীয় ফিশন বিক্রিয়ায় শক্তি উৎপাদন (সমস্যা 7)</t>
+          <t>বোর পরমাণু মডেল ও হাইড্রোজেন বর্ণালী (Bohr Model &amp; Spectra)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3981,29 +3729,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: নিউক্লীয় ফিশন বিক্রিয়ায় শক্তি উৎপাদন]
-একটি ইউরেনিয়াম (${}^{235}\text{U}$) নিউক্লিয়াসের ফিশনে প্রায় $200\text{ MeV}$ শক্তি নির্গত হয়। $1\text{ kg}$ ইউরেনিয়াম সম্পূর্ণ ফিশনে মোট কত জুল শক্তি পাওয়া যাবে?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+হাইড্রোজেন পরমাণুর ইলেকট্রনের গতিশক্তি $K$, স্থিতিশক্তি $U$ এবং মোট শক্তি $E$-এর মধ্যকার সম্পর্ক কী? $n = 1$ স্তরে এদের প্রত্যেকের মান ইলেকট্রন ভোল্টে লিখ।</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 7)।</t>
+          <t>কুলম্ব আকর্ষণ ও কেন্দ্রমুখী বল হতে: $K = \frac{k e^2}{2r}$, $U = -\frac{k e^2}{r} = -2K$। মোট শক্তি $E = K + U = K - 2K = -K$। সুতরাং $E = \frac{1}{2}U = -K$। $n = 1$-এ $E = -13.6\text{ eV} \implies K = +13.6\text{ eV}$ এবং $U = -27.2\text{ eV}$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>$K = -E = +13.6\text{ eV}, U = 2E = -27.2\text{ eV}, E = -13.6\text{ eV}$ ($K : U : E = 1 : -2 : -1$)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4023,12 +3771,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>বোর কক্ষপথে ইলেকট্রনের বেগ ও দ্রুতি (সমস্যা 8)</t>
+          <t>বোর পরমাণু মডেল ও হাইড্রোজেন বর্ণালী (Bohr Model &amp; Spectra)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4036,25 +3784,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: বোর কক্ষপথে ইলেকট্রনের বেগ ও দ্রুতি]
-হাইড্রোজেন পরমাণুর ১ম কক্ষপথে ইলেকট্রনের দ্রুতি $v_1 = 2.18 \times 10^6\text{ m/s}$ হলে 6-তম কক্ষপথে ইলেকট্রনের দ্রুতি ($v_n = v_1/n$) এবং প্রতি সেকেন্ডে ঘূর্ণন সংখ্যা কত?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+রাদারফোর্ডের আলফা কণা বিচ্ছুরণ পরীক্ষায় স্বর্ণপাতের ($Z = 79$) দিকে ধাবমান $K_lpha = 7.7\text{ MeV}$ গতিশক্তির একটি আলফা কণার নিকটতম পৌঁছানোর দূরত্ব (Distance of closest approach $r_0$) কত?</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 8)।</t>
+          <t>নিকটতম বিন্দুতে সমস্ত গতিশক্তি তড়িৎ স্থিতিশক্তিতে রূপান্তরিত হয়: $K_\alpha = \frac{1}{4\pi\epsilon_0}\frac{(2e)(Z e)}{r_0} \implies r_0 = \frac{2 k Z e^2}{K_\alpha}$। $K_\alpha = 7.7 \times 10^6 \times 1.6 \times 10^{-19}\text{ J} = 1.232 \times 10^{-12}\text{ J}$। $r_0 = \frac{2(9.0 \times 10^9) \times 79 \times (1.6 \times 10^{-19})^2}{1.232 \times 10^{-12}} = \frac{1.422 \times 10^{12} \times 2.56 \times 10^{-38}}{1.232 \times 10^{-12}} = \frac{3.640 \times 10^{-26}}{1.232 \times 10^{-12}} \approx 2.955 \times 10^{-14}\text{ m} = 29.55\text{ fm}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>নিকটতম দূরত্ব $r_0 = 2.95 \times 10^{-14}\text{ m} = 29.5\text{ fm}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4074,7 +3822,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় আলফা ও বিটা ক্ষয় সমীকরণ (সমস্যা 9)</t>
+          <t>বোর পরমাণু মডেল ও হাইড্রোজেন বর্ণালী (Bohr Model &amp; Spectra)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4083,29 +3831,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: তেজস্ক্রিয় আলফা ও বিটা ক্ষয় সমীকরণ]
-একটি তেজস্ক্রিয় রেডিয়াম নিউক্লিয়াস (${}^{226}_{88}\text{Ra}$) হতে একটি $\alpha$-কণা এবং দুটি $\beta$-কণা নির্গত হলে নতুন উৎপন্ন নিউক্লিয়াসের পারমাণবিক সংখ্যা ও ভর সংখ্যা কত হবে?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+বোর মডেলের দুটি প্রধান সীমাবদ্ধতা কী কী এবং এটি কেন জিম্যান প্রভাব (Zeeman effect) ও স্টার্ক প্রভাব (Stark effect) ব্যাখ্যা করতে পারে না?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 9)।</t>
+          <t>বোর মডেল কেবল একক ইলেকট্রনযুক্ত সিস্টেমে ($H, He^+, Li^{2+}$) প্রযোজ্য; একাধিক ইলেকট্রনের পারস্পরিক কুলম্ব বিকর্ষণ এতে বিবেচনা করা হয়নি। তাছাড়া বোর কক্ষপথকে দ্বিমাত্রিক বৃত্তাকার ধরায় কক্ষীয় কৌণিক ভরবেগের ত্রিমাত্রিক কোয়ান্টাইজেশন এবং ইলেকট্রনের নিজস্ব ঘূর্ণন বা স্পিন (Spin) এতে অনুপস্থিত ছিল। ফলে বাহ্যিক চৌম্বক ক্ষেত্রে স্পিন-অরবিট সংযোগের কারণে বর্ণালী রেখার বিভাজন (Zeeman effect) বোর মডেল দ্বারা ব্যাখ্যা করা অসম্ভব।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(১) একাধিক ইলেকট্রনযুক্ত জটিল পরমাণুর বর্ণালী ব্যাখ্যা করতে পারে না, (২) চৌম্বক ক্ষেত্র (জিম্যান) ও তড়িৎ ক্ষেত্রে (স্টার্ক) বর্ণালী রেখার সূক্ষ্ম বিভাজন ব্যাখ্যায় ব্যর্থ</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4125,12 +3873,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>নিউক্লীয় ফিউশন ও নক্ষত্রের সৌর শক্তি (সমস্যা 10)</t>
+          <t>বোর পরমাণু মডেল ও হাইড্রোজেন বর্ণালী (Bohr Model &amp; Spectra)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4138,25 +3886,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: নিউক্লীয় ফিউশন ও নক্ষত্রের সৌর শক্তি]
-সূর্যের অভ্যন্তরে ৪টি প্রোটন যুক্ত হয়ে ১টি হিলিয়াম নিউক্লিয়াস তৈরির সময় প্রায় $26.7\text{ MeV}$ শক্তি নির্গত হয়। প্রতি গ্রাম হাইড্রোজেন ফিউশনে কী পরিমাণ শক্তি নির্গত হবে?</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+প্যাশান সিরিজের (Paschen series, $n_1 = 3$) সবচেয়ে ছোট তরঙ্গদৈর্ঘ্য কত? এটি কি দৃশ্যমান, অবলোহিত (IR) নাকি অতিবেগুনী (UV) অঞ্চলে অবস্থিত?</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 10)।</t>
+          <t>$n_1 = 3, n_2 \to \infty$: $\frac{1}{\lambda} = R_H\left(\frac{1}{9} - 0\right) = \frac{R_H}{9} \implies \lambda = \frac{9}{R_H} = \frac{9}{1.097 \times 10^7} \approx 8.204 \times 10^{-7}\text{ m} = 820.4\text{ nm}$। দৃশ্যমান আলোর সীমা ৪০০-৭০০ ন্যানোমিটার; $820.4\text{ nm} &gt; 700\text{ nm}$ হওয়ায় এটি অবলোহিত (Infrared) অঞ্চলে অবস্থিত।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>সবচেয়ে ছোট তরঙ্গদৈর্ঘ্য $\lambda = 820.4\text{ nm}$, এটি অবলোহিত (Infrared, IR) অঞ্চলে অবস্থিত</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4176,44 +3924,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>বোর পরমাণু মডেল ও কক্ষপথের শক্তি (সমস্যা 11)</t>
+          <t>নিউক্লিয়াসের ধর্ম, ভর ত্রুটি ও বন্ধন শক্তি (Nuclear Structure &amp; Binding Energy)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>##PRESET:bohr-atom[size:medium]##
-[সমস্যা 11: বোর পরমাণু মডেল ও কক্ষপথের শক্তি]
-##PRESET:bohr-atom[size:medium]##
-হাইড্রোজেন পরমাণুর ভূমিস্তরের শক্তি $E_1 = -13.6\text{ eV}$। বোরের স্বীকার্যানুসারে 4-তম কক্ষপথের শক্তি ($E_n = E_1/n^2$) এবং কক্ষপথের ব্যাসার্ধ ($r_n = n^2 r_1$) কত? ($r_1 = 0.53\text{ \AA}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি লোহার নিউক্লিয়াসের ভর সংখ্যা $A = 56$। নিউক্লিয়াসটির ব্যাসার্ধ $R$ এবং নিউক্লিয়ার পদার্থের ঘনত্ব $+ho_{\text{nuc}}$ নির্ণয় কর। ($R_0 = 1.2\text{ fm} = 1.2 \times 10^{-15}\text{ m}$, গড় নিউক্লিয়ন ভর $m = 1.66 \times 10^{-27}\text{ kg}$)।</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>##PRESET:bohr-atom[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 11)।</t>
+          <t>নিউক্লীয় ব্যাসার্ধ $R = R_0 A^{1/3} = (1.2\text{ fm}) \times (56)^{1/3} = 1.2 \times 3.826 \approx 4.591\text{ fm} = 4.591 \times 10^{-15}\text{ m}$। নিউক্লিয়াসের আয়তন $V = \frac{4}{3}\pi R^3 = \frac{4}{3}\pi R_0^3 A$। মোট ভর $M = A \times m$। ঘনত্ব $\rho_{\text{nuc}} = \frac{M}{V} = \frac{m}{\frac{4}{3}\pi R_0^3} = \frac{1.66 \times 10^{-27}}{\frac{4}{3}\pi (1.2 \times 10^{-15})^3} = \frac{1.66 \times 10^{-27}}{7.238 \times 10^{-45}} \approx 2.293 \times 10^{17}\text{ kg/m}^3$। লক্ষণীয় যে ঘনত্ব ভর সংখ্যা $A$-এর ওপর সম্পূর্ণ স্বাধীন সার্বজনীন ধ্রুবক।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>ব্যাসার্ধ $R = 4.59\text{ fm} = 4.59 \times 10^{-15}\text{ m}$, ঘনত্ব $\rho_{\text{nuc}} = 2.29 \times 10^{17}\text{ kg/m}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4233,7 +3976,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় ক্ষয় ধ্রুবক ও অর্ধায়ু (সমস্যা 12)</t>
+          <t>নিউক্লিয়াসের ধর্ম, ভর ত্রুটি ও বন্ধন শক্তি (Nuclear Structure &amp; Binding Energy)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4246,31 +3989,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>##PRESET:decay-curve[size:medium]##
-[সমস্যা 12: তেজস্ক্রিয় ক্ষয় ধ্রুবক ও অর্ধায়ু]
-##PRESET:decay-curve[size:medium]##
-একটি তেজস্ক্রিয় আইসোটোপের অর্ধায়ু $T_{1/2} = 5.0\text{ দিন}$। মৌলটির ক্ষয় ধ্রুবক ($\lambda$) কত এবং কত দিন পর প্রাথমিক তেজস্ক্রিয় পরমাণুর মাত্র $6.25\%$ অবশিষ্ট থাকবে?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি হিলিয়াম নিউক্লিয়াসের ($_2^4\text{He}$) ভর $4.0015\text{ u}$। একটি প্রোটনের ভর $m_p = 1.0073\text{ u}$ এবং নিউট্রনের ভর $m_n = 1.0087\text{ u}$। হিলিয়াম নিউক্লিয়াসের ভর ত্রুটি (Mass defect $\Delta m$), মোট বন্ধন শক্তি (Binding energy $BE$) এবং নিউক্লিয়ন প্রতি বন্ধন শক্তি ($BE/A$) নির্ণয় কর। ($1\text{ u} = 931.5\text{ MeV}$)।</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:decay-curve[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 12)।</t>
+          <t>নিউক্লিয়নের মোট ভর $= 2 m_p + 2 m_n = 2(1.0073) + 2(1.0087) = 2.0146 + 2.0174 = 4.0320\text{ u}$। ভর ত্রুটি $\Delta m = 4.0320 - 4.0015 = 0.0305\text{ u}$। মোট বন্ধন শক্তি $BE = \Delta m \times 931.5\text{ MeV} = 0.0305 \times 931.5 \approx 28.41\text{ MeV}$। নিউক্লিয়ন প্রতি বন্ধন শক্তি $\frac{BE}{A} = \frac{28.41}{4} \approx 7.103\text{ MeV/nucleon}$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>ভর ত্রুটি $\Delta m = 0.0305\text{ u}$, মোট বন্ধন শক্তি $BE = 28.41\text{ MeV}$, প্রতি নিউক্লিয়নে $BE/A = 7.10\text{ MeV/nucleon}$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4290,38 +4027,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>হাইড্রোজেন বর্ণালীর বামার ও লাইম্যান সিরিজ (সমস্যা 13)</t>
+          <t>নিউক্লিয়াসের ধর্ম, ভর ত্রুটি ও বন্ধন শক্তি (Nuclear Structure &amp; Binding Energy)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: হাইড্রোজেন বর্ণালীর বামার ও লাইম্যান সিরিজ]
-হাইড্রোজেনের একটি ইলেকট্রন $n = 6$ শক্তিস্তর হতে $n = 2$ স্তরে লাফ দিলে নির্গত ফোটনের তরঙ্গদৈর্ঘ্য কত হবে? (রিডবার্গ ধ্রুবক $R_H = 1.097 \times 10^7\text{ m}^{-1}$)</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+বন্ধন শক্তি বক্ররেখা (Binding Energy Curve): প্রতি নিউক্লিয়ন বন্ধন শক্তির সর্বোচ্চ মান কোন মৌলের ক্ষেত্রে পরিলক্ষিত হয় এবং হালকা মৌলসমূহের ফিউশন ও ভারী মৌলসমূহের ফিশন কেন শক্তি নির্গমন করে?</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 13)।</t>
+          <t>$_26^{56}\text{Fe}$ সবচেয়ে সুস্থিত নিউক্লিয়াস যার $BE/A \approx 8.8\text{ MeV}$। হালকা নিউক্লিয়াসগুলোর ($A &lt; 20$) $BE/A$ কম ($\approx 7\text{ MeV}$) হওয়ায় এরা ফিউশনের মাধ্যমে যুক্ত হয়ে অধিক স্থিতিশীল ভারী নিউক্লিয়াসে পরিণত হলে ভর ত্রুটি সৃষ্টি করে প্রচুর শক্তি নির্গত করে। অন্যদিকে খুব ভারী ইউরেনিয়াম ($A \approx 235$, $BE/A \approx 7.6\text{ MeV}$) ফিশনে ভেঙে মাঝারি সুস্থিত খণ্ডে ($A \approx 100-140$, $BE/A \approx 8.5\text{ MeV}$) পরিণত হলে বন্ধন শক্তি বৃদ্ধি পাওয়ায় শক্তি নির্গত হয়।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>লোহার ($_26^{56}\text{Fe}$) ক্ষেত্রে সর্বোচ্চ $\approx 8.79\text{ MeV/nucleon}$; কম $BE/A$ হতে উচ্চ $BE/A$-এর দিকে রূপান্তরের ফলে উভয় প্রক্রিয়ায় শক্তি নির্গত হয়</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4341,7 +4078,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>নিউক্লিয়াসের বন্ধন শক্তি ও ভর ত্রুটি (সমস্যা 14)</t>
+          <t>নিউক্লিয়াসের ধর্ম, ভর ত্রুটি ও বন্ধন শক্তি (Nuclear Structure &amp; Binding Energy)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4354,25 +4091,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[সমস্যা 14: নিউক্লিয়াসের বন্ধন শক্তি ও ভর ত্রুটি]
-একটি হিলিয়াম নিউক্লিয়াসের (${}_2^4\text{He}$) ভর $4.0015\text{ u}$। দুটি প্রোটন ও দুটি নিউট্রনের মোট ভর $4.0319\text{ u}$ হলে ভর ত্রুটি এবং প্রতি নিউক্লিয়ন বন্ধন শক্তি কত মেগা-ইলেকট্রন ভোল্ট (MeV)? ($1\text{ u} = 931.5\text{ MeV}$)</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ইউরেনিয়াম-২৩৫ ($_92^{235}\text{U}$) নিউক্লিয়াসের ফিশনে গড়ে $200\text{ MeV}$ শক্তি নির্গত হয়। $1.0\text{ kg}$ ইউরেনিয়াম-২৩৫ সম্পূর্ণ ফিশন বিক্রিয়ায় রূপান্তরিত হলে মোট কত জুল শক্তি পাওয়া যাবে? এটি কত টন কয়লার সমতুল্য? ($1\text{ টন কয়লা} pprox 3.0 	imes 10^{10}\text{ J}$)।</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 14)।</t>
+          <t>১ কেজি ইউরেনিয়ামে পরমাণু সংখ্যা $N = \frac{1000\text{ g}}{235\text{ g/mol}} \times 6.022 \times 10^{23} \approx 2.5625 \times 10^{24}$ টি। মোট নির্গত শক্তি $E = N \times 200\text{ MeV} = (2.5625 \times 10^{24}) \times (200 \times 10^6 \times 1.6 \times 10^{-19}\text{ J}) = (2.5625 \times 10^{24}) \times (3.20 \times 10^{-11}\text{ J}) \approx 8.20 \times 10^{13}\text{ J}$। কয়লার সমতুল্য $= \frac{8.20 \times 10^{13}}{3.0 \times 10^{10}} \approx 2733.3\text{ টন}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>মোট শক্তি $E = 8.20 \times 10^{13}\text{ J}$, প্রায় $2733$ টন কয়লার সমতুল্য</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4392,38 +4129,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় নমুনার সক্রিয়তা (Activity) (সমস্যা 15)</t>
+          <t>নিউক্লিয়াসের ধর্ম, ভর ত্রুটি ও বন্ধন শক্তি (Nuclear Structure &amp; Binding Energy)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: তেজস্ক্রিয় নমুনার সক্রিয়তা (Activity)]
-একটি তেজস্ক্রিয় নমুনার ক্ষয় ধ্রুবক $\lambda = 0.03\text{ s}^{-1}$ এবং এতে উপস্থিত অবিঘটিত পরমাণুর সংখ্যা $N = 8 \times 10^{18}$। নমুনাটির বর্তমান সক্রিয়তা কত কুরি (Curie)? ($1\text{ Ci} = 3.7 \times 10^{10}\text{ Bq}$)</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ডিউটেরন ($m_d = 2.0141\text{ u}$) ও একটি ট্রাইটন ($m_t = 3.0160\text{ u}$) যুক্ত হয়ে একটি আলফা কণা ($m_lpha = 4.0026\text{ u}$) এবং একটি নিউট্রন ($m_n = 1.0087\text{ u}$) উৎপন্ন করে (D-T fusion)। বিক্রিয়ার $Q$-মান কত $\text{MeV}$?</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 15)।</t>
+          <t>বিক্রিয়কের মোট ভর $M_i = 2.0141 + 3.0160 = 5.0301\text{ u}$। উৎপাদের মোট ভর $M_f = 4.0026 + 1.0087 = 5.0113\text{ u}$। ভর ত্রুটি $\Delta m = M_i - M_f = 5.0301 - 5.0113 = 0.0188\text{ u}$। শক্তি $Q = \Delta m \times 931.5\text{ MeV} = 0.0188 \times 931.5 \approx 17.512\text{ MeV}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>বিক্রিয়ার $Q$-মান $= 17.51\text{ MeV}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4443,7 +4180,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় গড় আয়ু ও অর্ধায়ু সম্পর্ক (সমস্যা 16)</t>
+          <t>নিউক্লিয়াসের ধর্ম, ভর ত্রুটি ও বন্ধন শক্তি (Nuclear Structure &amp; Binding Energy)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4456,25 +4193,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: তেজস্ক্রিয় গড় আয়ু ও অর্ধায়ু সম্পর্ক]
-একটি তেজস্ক্রিয় রেডিয়াম নমুনার গড় আয়ু $\tau = 400\text{ বছর}$। এর অর্ধায়ু ($T_{1/2} = 0.693\tau$) কত বছর হবে?</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+সবল নিউক্লীয় বলের (Strong Nuclear Force) চারটি প্রধান বৈশিষ্ট্য উল্লেখ কর। এটি কেন কুলম্বীয় বিকর্ষণ থাকা সত্ত্বেও প্রোটনগুলোকে নিউক্লিয়াসে আবদ্ধ রাখে?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 16)।</t>
+          <t>নিউক্লিয়াসের দূরত্বে ($r &lt; 1.5\text{ fm}$) সবল নিউক্লীয় আকর্ষণ বল দুটি প্রোটনের মধ্যবর্তী কুলম্বীয় স্থির তড়িৎ বিকর্ষণ বলের চেয়ে প্রায় ১০০ গুণ বেশি শক্তিশালী হয়। তবে $r &gt; 2\text{ fm}$-এ এটি দ্রুত শূন্যে নেমে যায়। এই অতি স্বল্প পাল্লায় প্রচণ্ড আকর্ষণের কারণেই বহু-প্রোটনবিশিষ্ট ভারী নিউক্লিয়াসও একত্রিত অবস্থায় টিকে থাকে।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(১) সবচেয়ে শক্তিশালী মৌলিক বল, (২) অতি স্বল্প পাল্লার ($\approx 1-2\text{ fm}$), (৩) আধান-নিরপেক্ষ ($p-p, n-n, p-n$ সমান), (৪) সম্পৃক্ত ধর্মী; নিউক্লীয় দূরত্বের মধ্যে এটি তড়িৎ বিকর্ষণের চেয়ে প্রায় ১০০ গুণ শক্তিশালী</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4494,38 +4231,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>নিউক্লীয় ফিশন বিক্রিয়ায় শক্তি উৎপাদন (সমস্যা 17)</t>
+          <t>নিউক্লিয়াসের ধর্ম, ভর ত্রুটি ও বন্ধন শক্তি (Nuclear Structure &amp; Binding Energy)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: নিউক্লীয় ফিশন বিক্রিয়ায় শক্তি উৎপাদন]
-একটি ইউরেনিয়াম (${}^{235}\text{U}$) নিউক্লিয়াসের ফিশনে প্রায় $200\text{ MeV}$ শক্তি নির্গত হয়। $1\text{ kg}$ ইউরেনিয়াম সম্পূর্ণ ফিশনে মোট কত জুল শক্তি পাওয়া যাবে?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+আইসোবার, আইসোটোপ এবং আইসোটোনের সংজ্ঞাগত পার্থক্য: $_{6}^{14}	ext{C}$ এবং $_{7}^{14}	ext{N}$ পরস্পরের কী? $_{6}^{12}	ext{C}$ এবং $_{6}^{14}	ext{C}$ পরস্পরের কী?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 17)।</t>
+          <t>আইসোটোপ: একই প্রোটন সংখ্যা ($Z$) কিন্তু ভিন্ন ভর সংখ্যা ($A$)। আইসোবার: একই ভর সংখ্যা ($A$) কিন্তু ভিন্ন পারমাণবিক সংখ্যা ($Z$)। আইসোটোন: সমান নিউট্রন সংখ্যা ($N = A - Z$)। যেমন $_{6}^{14}\text{C}$ এবং $_{7}^{14}\text{N}$-এর উভয়ের ভর সংখ্যা ১৪ হওয়ায় এরা আইসোবার।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>$_{6}^{14}\text{C}$ ও $_{7}^{14}\text{N}$ হলো আইসোবার (সমান ভর সংখ্যা $A=14$); $_{6}^{12}\text{C}$ ও $_{6}^{14}\text{C}$ হলো আইসোটোপ (সমান প্রোটন সংখ্যা $Z=6$)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4545,7 +4282,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>বোর কক্ষপথে ইলেকট্রনের বেগ ও দ্রুতি (সমস্যা 18)</t>
+          <t>নিউক্লিয়াসের ধর্ম, ভর ত্রুটি ও বন্ধন শক্তি (Nuclear Structure &amp; Binding Energy)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4558,25 +4295,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: বোর কক্ষপথে ইলেকট্রনের বেগ ও দ্রুতি]
-হাইড্রোজেন পরমাণুর ১ম কক্ষপথে ইলেকট্রনের দ্রুতি $v_1 = 2.18 \times 10^6\text{ m/s}$ হলে 6-তম কক্ষপথে ইলেকট্রনের দ্রুতি ($v_n = v_1/n$) এবং প্রতি সেকেন্ডে ঘূর্ণন সংখ্যা কত?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি নিউক্লিয়াসের ভর ত্রুটি বলতে কী বোঝায়? একটি নিউক্লিয়াসের প্রকৃত ভর তার পৃথক নিউক্লিয়নগুলোর ভরের যোগফলের চেয়ে কেন সর্বদা কম হয়?</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 18)।</t>
+          <t>পৃথক প্রোটন ও নিউট্রন যখন সবল নিউক্লীয় বল দ্বারা পরস্পরের সাথে আবদ্ধ হয়ে একটি স্থিতিশীল নিউক্লিয়াস তৈরি করে, তখন সিস্টেমটি নিম্ন শক্তি স্তরে নেমে আসে। নির্গত এই শক্তিকে বন্ধন শক্তি বলে। ভরের সংরক্ষণশীলতার আপেক্ষিক নীতি অনুসারে এই নির্গত শক্তির সমতুল্য ভর সিস্টেম হতে হারিয়ে যায় ($\Delta m = BE/c^2$), ফলে সমাপ্ত নিউক্লিয়াসের ভর উপাদান নিউক্লিয়নগুলোর ভরের চেয়ে কম হয়।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>নিউক্লিয়নগুলো একত্রিত হয়ে নিউক্লিয়াস গঠনের সময় বন্ধন শক্তি সমপরিমাণ ভর আইনস্টাইনের $E = \Delta m c^2$ সূত্রে শক্তিতে রূপান্তরিত হয়ে নির্গত হয়</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4596,38 +4333,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় আলফা ও বিটা ক্ষয় সমীকরণ (সমস্যা 19)</t>
+          <t>নিউক্লিয়াসের ধর্ম, ভর ত্রুটি ও বন্ধন শক্তি (Nuclear Structure &amp; Binding Energy)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: তেজস্ক্রিয় আলফা ও বিটা ক্ষয় সমীকরণ]
-একটি তেজস্ক্রিয় রেডিয়াম নিউক্লিয়াস (${}^{226}_{88}\text{Ra}$) হতে একটি $\alpha$-কণা এবং দুটি $\beta$-কণা নির্গত হলে নতুন উৎপন্ন নিউক্লিয়াসের পারমাণবিক সংখ্যা ও ভর সংখ্যা কত হবে?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি আলফা কণার বন্ধন শক্তি $28.3\text{ MeV}$ এবং একটি ডিউটেরনের বন্ধন শক্তি $2.2\text{ MeV}$। দুটি ডিউটেরন যুক্ত হয়ে একটি আলফা কণা গঠন করলে কত $\text{MeV}$ শক্তি নির্গত হবে?</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 19)।</t>
+          <t>বিক্রিয়া: $_1^2\text{H} + _1^2\text{H} \to _2^4\text{He} + Q$। প্রারম্ভিক মোট বন্ধন শক্তি $= 2 \times 2.2 = 4.4\text{ MeV}$। অন্তিম মোট বন্ধন শক্তি $= 28.3\text{ MeV}$। নির্গত শক্তি $Q = BE(\text{He}) - 2 BE(\text{H}) = 28.3 - 4.4 = 23.9\text{ MeV}$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>নির্গত শক্তি $Q = 23.9\text{ MeV}$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4647,7 +4384,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>নিউক্লীয় ফিউশন ও নক্ষত্রের সৌর শক্তি (সমস্যা 20)</t>
+          <t>নিউক্লিয়াসের ধর্ম, ভর ত্রুটি ও বন্ধন শক্তি (Nuclear Structure &amp; Binding Energy)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4660,25 +4397,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: নিউক্লীয় ফিউশন ও নক্ষত্রের সৌর শক্তি]
-সূর্যের অভ্যন্তরে ৪টি প্রোটন যুক্ত হয়ে ১টি হিলিয়াম নিউক্লিয়াস তৈরির সময় প্রায় $26.7\text{ MeV}$ শক্তি নির্গত হয়। প্রতি গ্রাম হাইড্রোজেন ফিউশনে কী পরিমাণ শক্তি নির্গত হবে?</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+নিউক্লীয় ফিশনে মডারেটর (Moderator) এবং নিয়ন্ত্রণ দণ্ডের (Control rod) কাজ কী? পারমাণবিক চুল্লিতে ভারী পানি বা গ্রাফাইট কেন মডারেটর হিসেবে ব্যবহার করা হয়?</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 20)।</t>
+          <t>ফিশনে নির্গত নিউট্রনগুলো অত্যন্ত দ্রুতগামী ($\approx 2\text{ MeV}$) হয়, কিন্তু $^{235}\text{U}$ কেবল ধীরগতির তাপীয় নিউট্রন ($\approx 0.025\text{ eV}$) দ্বারা সহজে ফিশন ঘটায়। হালকা নিউক্লিয়াসযুক্ত পদার্থ (যেমন ভারী পানি $\text{D}_2\text{O}$ বা গ্রাফাইট) স্থিতিস্থাপক সংঘর্ষের মাধ্যমে নিউট্রনের শক্তি দ্রুত শোষণ করে এর গতি কমিয়ে দেয় কিন্তু নিজেরা নিউট্রন শোষণ করে ধ্বংস করে না, ফলে এরা আদর্শ মডারেটর হিসেবে কাজ করে।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>মডারেটর দ্রুতগামী নিউট্রনের গতি কমিয়ে তাপীয় নিউট্রনে পরিণত করে; নিয়ন্ত্রণ দণ্ড (যেমন ক্যাডমিয়াম/বোরন) অতিরিক্ত নিউট্রন শোষণ করে চেইন রিঅ্যাকশন নিয়ন্ত্রণ করে</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4698,44 +4435,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>বোর পরমাণু মডেল ও কক্ষপথের শক্তি (সমস্যা 21)</t>
+          <t>তেজস্ক্রিয়তার ক্ষয় সূত্র, অর্ধায়ু ও সক্রিয়তা (Radioactive Decay &amp; Half-Life)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>##PRESET:bohr-atom[size:medium]##
-[সমস্যা 21: বোর পরমাণু মডেল ও কক্ষপথের শক্তি]
-##PRESET:bohr-atom[size:medium]##
-হাইড্রোজেন পরমাণুর ভূমিস্তরের শক্তি $E_1 = -13.6\text{ eV}$। বোরের স্বীকার্যানুসারে 4-তম কক্ষপথের শক্তি ($E_n = E_1/n^2$) এবং কক্ষপথের ব্যাসার্ধ ($r_n = n^2 r_1$) কত? ($r_1 = 0.53\text{ \AA}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তেজস্ক্রিয় মৌলের অর্ধায়ু (Half-life) $T_{1/2} = 1600\text{ বছর}$ (রেডিয়াম)। মৌলটির অবক্ষয় ধ্রুবক (Decay constant $\lambda$) এবং গড় আয়ু (Mean life $\tau$) নির্ণয় কর। $6400\text{ বছর}$ পর মৌলটির প্রারম্ভিক পরিমাণের কত অংশ অবশিষ্ট থাকবে?</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##PRESET:bohr-atom[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 21)।</t>
+          <t>$\lambda = \frac{\ln 2}{T_{1/2}} = \frac{0.69315}{1600\text{ yr}} \approx 4.332 \times 10^{-4}\text{ yr}^{-1}$। গড় আয়ু $\tau = \frac{1}{\lambda} = \frac{T_{1/2}}{0.69315} = \frac{1600}{0.69315} \approx 2308.3\text{ বছর}$। অর্ধায়ু সংখ্যা $n = \frac{t}{T_{1/2}} = \frac{6400}{1600} = 4$। অবশিষ্ট ভগ্নাংশ $\frac{N}{N_0} = \left(\frac{1}{2}\right)^n = \left(\frac{1}{2}\right)^4 = \frac{1}{16} = 0.0625 = 6.25\%$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>অবক্ষয় ধ্রুবক $\lambda = 4.33 \times 10^{-4}\text{ year}^{-1}$, গড় আয়ু $\tau = 2308.8\text{ বছর}$, অবশিষ্ট থাকবে $\frac{1}{16}$ অংশ ($6.25\%$ অংশ)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4755,7 +4486,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় ক্ষয় ধ্রুবক ও অর্ধায়ু (সমস্যা 22)</t>
+          <t>তেজস্ক্রিয়তার ক্ষয় সূত্র, অর্ধায়ু ও সক্রিয়তা (Radioactive Decay &amp; Half-Life)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4768,31 +4499,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>##PRESET:decay-curve[size:medium]##
-[সমস্যা 22: তেজস্ক্রিয় ক্ষয় ধ্রুবক ও অর্ধায়ু]
-##PRESET:decay-curve[size:medium]##
-একটি তেজস্ক্রিয় আইসোটোপের অর্ধায়ু $T_{1/2} = 5.0\text{ দিন}$। মৌলটির ক্ষয় ধ্রুবক ($\lambda$) কত এবং কত দিন পর প্রাথমিক তেজস্ক্রিয় পরমাণুর মাত্র $6.25\%$ অবশিষ্ট থাকবে?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তেজস্ক্রিয় নমুনায় প্রারম্ভে $N_0 = 1.0 	imes 10^{20}$ টি পরমাণু ছিল। মৌলটির অর্ধায়ু $10\text{ দিন}$ হলে $30\text{ দিন}$ সময়ে কতটি পরমাণু ক্ষয়প্রাপ্ত হবে এবং নমুনাটির প্রারম্ভিক সক্রিয়তা (Initial activity) কত বেকেরেল ($	ext{Bq}$)?</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>##PRESET:decay-curve[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 22)।</t>
+          <t>অর্ধায়ু সংখ্যা $n = 30/10 = 3$। অবশিষ্ট পরমাণু $N = N_0(1/2)^3 = \frac{N_0}{8} = 1.25 \times 10^{19}$। ক্ষয়প্রাপ্ত পরমাণু $\Delta N = N_0 - N = N_0\left(1 - \frac{1}{8}\right) = \frac{7}{8}N_0 = 0.875 \times 10^{20} = 8.75 \times 10^{19}$ টি। ক্ষয় ধ্রুবক $\lambda = \frac{0.69315}{10 \times 24 \times 3600\text{ s}} = \frac{0.69315}{864000} \approx 8.0226 \times 10^{-7}\text{ s}^{-1}$। সক্রিয়তা $A_0 = \lambda N_0 = (8.0226 \times 10^{-7}) \times 10^{20} = 8.023 \times 10^{13}\text{ Bq}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>ক্ষয়প্রাপ্ত পরমাণু সংখ্যা $\Delta N = 8.75 \times 10^{19}$ টি, প্রারম্ভিক সক্রিয়তা $A_0 = 8.02 \times 10^{13}\text{ Bq} \approx 2168.0\text{ Ci}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4812,38 +4537,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>হাইড্রোজেন বর্ণালীর বামার ও লাইম্যান সিরিজ (সমস্যা 23)</t>
+          <t>তেজস্ক্রিয়তার ক্ষয় সূত্র, অর্ধায়ু ও সক্রিয়তা (Radioactive Decay &amp; Half-Life)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: হাইড্রোজেন বর্ণালীর বামার ও লাইম্যান সিরিজ]
-হাইড্রোজেনের একটি ইলেকট্রন $n = 6$ শক্তিস্তর হতে $n = 2$ স্তরে লাফ দিলে নির্গত ফোটনের তরঙ্গদৈর্ঘ্য কত হবে? (রিডবার্গ ধ্রুবক $R_H = 1.097 \times 10^7\text{ m}^{-1}$)</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তেজস্ক্রিয় নমুনার সক্রিয়তা $30\text{ দিনে}$ কমে তার আদি সক্রিয়তার এক-অষ্টমাংশ ($1/8$) হয়। মৌলটির অর্ধায়ু এবং অবক্ষয় ধ্রুবক কত?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 23)।</t>
+          <t>সক্রিয়তা $A(t) = A_0 e^{-\lambda t} = A_0(1/2)^n = \frac{A_0}{8} = A_0\left(\frac{1}{2}\right)^3$। ফলে অর্ধায়ু সংখ্যা $n = 3$। অর্ধায়ু $T_{1/2} = \frac{t}{n} = \frac{30\text{ দিন}}{3} = 10.0\text{ দিন}$। ক্ষয় ধ্রুবক $\lambda = \frac{0.69315}{10} = 0.069315\text{ day}^{-1}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>অর্ধায়ু $T_{1/2} = 10.0\text{ দিন}$, অবক্ষয় ধ্রুবক $\lambda = 0.0693\text{ day}^{-1}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4863,7 +4588,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>নিউক্লিয়াসের বন্ধন শক্তি ও ভর ত্রুটি (সমস্যা 24)</t>
+          <t>তেজস্ক্রিয়তার ক্ষয় সূত্র, অর্ধায়ু ও সক্রিয়তা (Radioactive Decay &amp; Half-Life)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4876,25 +4601,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: নিউক্লিয়াসের বন্ধন শক্তি ও ভর ত্রুটি]
-একটি হিলিয়াম নিউক্লিয়াসের (${}_2^4\text{He}$) ভর $4.0015\text{ u}$। দুটি প্রোটন ও দুটি নিউট্রনের মোট ভর $4.0319\text{ u}$ হলে ভর ত্রুটি এবং প্রতি নিউক্লিয়ন বন্ধন শক্তি কত মেগা-ইলেকট্রন ভোল্ট (MeV)? ($1\text{ u} = 931.5\text{ MeV}$)</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি প্রত্নতাত্ত্বিক কাঠের নমুনায় প্রতি গ্রাম কার্বনে প্রতি মিনিটে $C^{14}$-এর সক্রিয়তা পাওয়া গেল $3.75\text{ count/min}$। একটি জীবিত উদ্ভিদের কাঠে এই সক্রিয়তা $15.0\text{ count/min}$। $C^{14}$-এর অর্ধায়ু $5730\text{ বছর}$ হলে কাঠের নমুনাটির বয়স (Age of fossil) কত?</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 24)।</t>
+          <t>সক্রিয়তা অনুপাত $\frac{A}{A_0} = \frac{3.75}{15.0} = \frac{1}{4} = \left(\frac{1}{2}\right)^2$। অর্থাৎ নমুনাটির বয়স দুটি অর্ধায়ুর সমান: $t = 2 \times T_{1/2} = 2 \times 5730 = 11460\text{ বছর}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>নমুনাটির বয়স $t = 11460\text{ বছর}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4914,38 +4639,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় নমুনার সক্রিয়তা (Activity) (সমস্যা 25)</t>
+          <t>তেজস্ক্রিয়তার ক্ষয় সূত্র, অর্ধায়ু ও সক্রিয়তা (Radioactive Decay &amp; Half-Life)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: তেজস্ক্রিয় নমুনার সক্রিয়তা (Activity)]
-একটি তেজস্ক্রিয় নমুনার ক্ষয় ধ্রুবক $\lambda = 0.03\text{ s}^{-1}$ এবং এতে উপস্থিত অবিঘটিত পরমাণুর সংখ্যা $N = 4 \times 10^{18}$। নমুনাটির বর্তমান সক্রিয়তা কত কুরি (Curie)? ($1\text{ Ci} = 3.7 \times 10^{10}\text{ Bq}$)</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তেজস্ক্রিয় মৌল ক্ষয়প্রাপ্ত হয়ে তার মূল পরিমাণের $90\%$ ক্ষয় হতে কত সময় লাগবে? (মৌলটির অর্ধায়ু $T$)।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 25)।</t>
+          <t>$90\%$ ক্ষয় হলে অবশিষ্ট থাকে $10\%$: $N = 0.10 N_0$। তেজস্ক্রিয় সমীকরণ: $N = N_0 e^{-\lambda t} \implies 0.10 = e^{-\lambda t} \implies \lambda t = \ln(10) \approx 2.3026$। আবার $\lambda = \frac{\ln 2}{T} = \frac{0.69315}{T}$। অতএব $t = \frac{2.3026}{\lambda} = \frac{2.3026}{0.69315} T \approx 3.322 T$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>সময় $t = 3.32 T$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4965,7 +4690,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় গড় আয়ু ও অর্ধায়ু সম্পর্ক (সমস্যা 26)</t>
+          <t>তেজস্ক্রিয়তার ক্ষয় সূত্র, অর্ধায়ু ও সক্রিয়তা (Radioactive Decay &amp; Half-Life)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4978,25 +4703,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: তেজস্ক্রিয় গড় আয়ু ও অর্ধায়ু সম্পর্ক]
-একটি তেজস্ক্রিয় রেডিয়াম নমুনার গড় আয়ু $\tau = 400\text{ বছর}$। এর অর্ধায়ু ($T_{1/2} = 0.693\tau$) কত বছর হবে?</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তেজস্ক্রিয় মৌল দুটি ভিন্ন প্রক্রিয়ায় ক্ষয়প্রাপ্ত হয় যাদের পৃথক ক্ষয় ধ্রুবক যথাক্রমে $\lambda_1 = 0.02\text{ hr}^{-1}$ এবং $\lambda_2 = 0.03\text{ hr}^{-1}$। মৌলটির কার্যকর মোট ক্ষয় ধ্রুবক $\lambda_{\text{eff}}$ এবং কার্যকর অর্ধায়ু কত?</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 26)।</t>
+          <t>সমান্তরাল ক্ষয় প্রক্রিয়ায় মোট ক্ষয় ধ্রুবক যোগ হয়: $\lambda_{\text{eff}} = \lambda_1 + \lambda_2 = 0.02 + 0.03 = 0.05\text{ hr}^{-1}$। কার্যকর অর্ধায়ু $T_{\text{eff}} = \frac{\ln 2}{\lambda_{\text{eff}}} = \frac{0.69315}{0.05} = 13.863\text{ hr}$ (বা $\frac{1}{T_{\text{eff}}} = \frac{1}{T_1} + \frac{1}{T_2}$)।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>কার্যকর ক্ষয় ধ্রুবক $\lambda_{\text{eff}} = 0.05\text{ hr}^{-1}$, কার্যকর অর্ধায়ু $T_{\text{eff}} = 13.86\text{ ঘণ্টা}$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5016,38 +4741,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>নিউক্লীয় ফিশন বিক্রিয়ায় শক্তি উৎপাদন (সমস্যা 27)</t>
+          <t>তেজস্ক্রিয়তার ক্ষয় সূত্র, অর্ধায়ু ও সক্রিয়তা (Radioactive Decay &amp; Half-Life)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: নিউক্লীয় ফিশন বিক্রিয়ায় শক্তি উৎপাদন]
-একটি ইউরেনিয়াম (${}^{235}\text{U}$) নিউক্লিয়াসের ফিশনে প্রায় $200\text{ MeV}$ শক্তি নির্গত হয়। $1\text{ kg}$ ইউরেনিয়াম সম্পূর্ণ ফিশনে মোট কত জুল শক্তি পাওয়া যাবে?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+আলফা ক্ষয়, বিটা ঋণাত্মক ক্ষয় এবং গামা ক্ষয়ের ফলে আদি নিউক্লিয়াসের পারমাণবিক সংখ্যা $Z$ এবং ভর সংখ্যা $A$-এর কী পরিবর্তন ঘটে?</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 27)।</t>
+          <t>$\alpha$-কণা হলো হিলিয়াম নিউক্লিয়াস ($_2^4\text{He}$), ফলে ২ একক প্রোটন ও ৪ একক ভর কমে। $\beta^-$-ক্ষয়ে নিউক্লিয়াসের একটি নিউট্রন প্রোটনে রূপান্তরিত হয় ($n \to p + e^- + \bar{\nu}_e$), ফলে $Z$ ১ বৃদ্ধি পায় কিন্তু ভর সংখ্যা $A$ অপরিবর্তিত থাকে। $\gamma$-রশ্মি হলো উচ্চ শক্তির ফোটন বিকিরণ, যা উত্তেজিত নিউক্লিয়াসকে অতিরিক্ত শক্তি বর্জন করে নিম্ন শক্তিতে আনে কিন্তু $Z$ বা $A$-এর কোনো পরিবর্তন করে না।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>$\alpha$-ক্ষয়: $Z \to Z-2, A \to A-4$; $\beta^-$-ক্ষয়: $Z \to Z+1, A \to A$; $\gamma$-নিঃসরণ: $Z$ ও $A$ উভয়ই অপরিবর্তিত থাকে</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5067,7 +4792,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>বোর কক্ষপথে ইলেকট্রনের বেগ ও দ্রুতি (সমস্যা 28)</t>
+          <t>তেজস্ক্রিয়তার ক্ষয় সূত্র, অর্ধায়ু ও সক্রিয়তা (Radioactive Decay &amp; Half-Life)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5080,25 +4805,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: বোর কক্ষপথে ইলেকট্রনের বেগ ও দ্রুতি]
-হাইড্রোজেন পরমাণুর ১ম কক্ষপথে ইলেকট্রনের দ্রুতি $v_1 = 2.18 \times 10^6\text{ m/s}$ হলে 6-তম কক্ষপথে ইলেকট্রনের দ্রুতি ($v_n = v_1/n$) এবং প্রতি সেকেন্ডে ঘূর্ণন সংখ্যা কত?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তেজস্ক্রিয় আইসোটোপ $_{92}^{238}	ext{U}$ পর পর কয়েকটি $lpha$ ও $eta$ ক্ষয়ের পর সুস্থিত $_{82}^{206}	ext{Pb}$-এ পরিণত হলো। এই ক্ষয় শৃঙ্খলে মোট কতটি $lpha$-কণা এবং কতটি $eta^-$-কণা নিঃসৃত হয়েছে?</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 28)।</t>
+          <t>ভর সংখ্যার পরিবর্তন কেবল $\alpha$-কণার কারণে হয়: $\Delta A = 238 - 206 = 32$। প্রতি $\alpha$-কণায় ৪ ভর কমায় $\alpha$-কণার সংখ্যা $n_\alpha = \frac{32}{4} = 8$ টি। ৮টি $\alpha$ ক্ষয়ে প্রোটন সংখ্যা কমে $8 \times 2 = 16$, ফলে প্রোটন সংখ্যা হওয়ার কথা ছিল $92 - 16 = 76$। কিন্তু সীসার প্রোটন সংখ্যা $82$। প্রোটন বৃদ্ধির কারণ $\beta^-$ ক্ষয়: $n_\beta = 82 - 76 = 6$ টি।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>মোট $8$টি $\alpha$-কণা এবং $6$টি $\beta^-$-কণা নিঃসৃত হয়েছে</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5118,38 +4843,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় আলফা ও বিটা ক্ষয় সমীকরণ (সমস্যা 29)</t>
+          <t>তেজস্ক্রিয়তার ক্ষয় সূত্র, অর্ধায়ু ও সক্রিয়তা (Radioactive Decay &amp; Half-Life)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: তেজস্ক্রিয় আলফা ও বিটা ক্ষয় সমীকরণ]
-একটি তেজস্ক্রিয় রেডিয়াম নিউক্লিয়াস (${}^{226}_{88}\text{Ra}$) হতে একটি $\alpha$-কণা এবং দুটি $\beta$-কণা নির্গত হলে নতুন উৎপন্ন নিউক্লিয়াসের পারমাণবিক সংখ্যা ও ভর সংখ্যা কত হবে?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তেজস্ক্রিয় নমুনার আদি সক্রিয়তা $1.0\text{ Curie}$ ($1\text{ Ci} = 3.7 	imes 10^{10}\text{ Bq}$)। এর অর্ধায়ু $5.0\text{ দিন}$ হলে ২০ দিন পর এর সক্রিয়তা কত মিলিকুরি ($	ext{mCi}$) হবে?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 29)।</t>
+          <t>অর্ধায়ুর সংখ্যা $n = \frac{20}{5.0} = 4$। অবশিষ্ট সক্রিয়তা $A = A_0 \left(\frac{1}{2}\right)^4 = \frac{1.0\text{ Ci}}{16} = 0.0625\text{ Ci} = 62.5\text{ mCi}$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>সক্রিয়তা $A = 62.5\text{ mCi}$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5169,7 +4894,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>নিউক্লীয় ফিউশন ও নক্ষত্রের সৌর শক্তি (সমস্যা 30)</t>
+          <t>তেজস্ক্রিয়তার ক্ষয় সূত্র, অর্ধায়ু ও সক্রিয়তা (Radioactive Decay &amp; Half-Life)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5182,25 +4907,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: নিউক্লীয় ফিউশন ও নক্ষত্রের সৌর শক্তি]
-সূর্যের অভ্যন্তরে ৪টি প্রোটন যুক্ত হয়ে ১টি হিলিয়াম নিউক্লিয়াস তৈরির সময় প্রায় $26.7\text{ MeV}$ শক্তি নির্গত হয়। প্রতি গ্রাম হাইড্রোজেন ফিউশনে কী পরিমাণ শক্তি নির্গত হবে?</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+তেজস্ক্রিয় সাম্যাবস্থা (Radioactive Secular Equilibrium): দীর্ঘায়ু বিশিষ্ট একটি জনক নিউক্লিয়াস $A$ ক্ষয় হয়ে স্বল্পায়ু বিশিষ্ট দুহিতা নিউক্লিয়াস $B$-তে এবং $B$ ক্ষয় হয়ে সুস্থিত $C$-তে পরিণত হচ্ছে। দীর্ঘ সময় পর $A$ ও $B$-এর পরমাণু সংখ্যার অনুপাত $rac{N_A}{N_B}$ তাদের অর্ধায়ুর সাথে কীভাবে সম্পর্কিত?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 30)।</t>
+          <t>তেজস্ক্রিয় সাম্যাবস্থায় দুহিতা নিউক্লিয়াস উৎপাদনের হার এবং এর ক্ষয়ের হার সমান হয়: $\frac{dN_B}{dt} = \lambda_A N_A - \lambda_B N_B = 0 \implies \lambda_A N_A = \lambda_B N_B$। ফলে সক্রিয়তা সমান থাকে এবং পরমাণু সংখ্যার অনুপাত অর্ধায়ুর সমানুপাতিক হয়: $\frac{N_A}{N_B} = \frac{\lambda_B}{\lambda_A} = \frac{T_{1/2}(A)}{T_{1/2}(B)}$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>$\frac{N_A}{N_B} = \frac{\lambda_B}{\lambda_A} = \frac{T_{1/2}(A)}{T_{1/2}(B)}$, অর্থাৎ উভয়ের সক্রিয়তা সমান হয় ($\lambda_A N_A = \lambda_B N_B$)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5220,44 +4945,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>বোর পরমাণু মডেল ও কক্ষপথের শক্তি (সমস্যা 31)</t>
+          <t>উন্নত নিউক্লীয় বিক্রিয়া, শক্তি ও ফিশন-ফিউশন (Nuclear Reactions &amp; Q-Value)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>##PRESET:bohr-atom[size:medium]##
-[সমস্যা 31: বোর পরমাণু মডেল ও কক্ষপথের শক্তি]
-##PRESET:bohr-atom[size:medium]##
-হাইড্রোজেন পরমাণুর ভূমিস্তরের শক্তি $E_1 = -13.6\text{ eV}$। বোরের স্বীকার্যানুসারে 4-তম কক্ষপথের শক্তি ($E_n = E_1/n^2$) এবং কক্ষপথের ব্যাসার্ধ ($r_n = n^2 r_1$) কত? ($r_1 = 0.53\text{ \AA}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি নিউক্লিয়ার বিক্রিয়া $_7^{14}	ext{N} + _2^4	ext{He} 	o _8^{17}	ext{O} + _1^1	ext{H}$। কণাগুলোর পারমাণবিক ভর যথাক্রমে: $m(	ext{N}) = 14.00307\text{ u}$, $m(	ext{He}) = 4.00260\text{ u}$, $m(	ext{O}) = 16.99913\text{ u}$, $m(	ext{H}) = 1.00783\text{ u}$। বিক্রিয়াটির $Q$-মান কত এবং বিক্রিয়াটি তাপোৎপাদী না তাপহারী?</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##PRESET:bohr-atom[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 31)।</t>
+          <t>বিক্রিয়কের মোট ভর $M_i = 14.00307 + 4.00260 = 18.00567\text{ u}$। উৎপাদের মোট ভর $M_f = 16.99913 + 1.00783 = 18.00696\text{ u}$। ভর ত্রুটি $\Delta m = M_i - M_f = 18.00567 - 18.00696 = -0.00129\text{ u}$। $Q$-মান $= \Delta m \times 931.5\text{ MeV} = -0.00129 \times 931.5 \approx -1.2016\text{ MeV}$। $Q &lt; 0$ হওয়ায় বিক্রিয়াটি তাপহারী, অর্থাৎ বিক্রিয়া ঘটাতে আপতিত $\alpha$-কণার ন্যূনতম কিছু গতিশক্তি (সূচনা শক্তি / Threshold energy) থাকতে হবে।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>$Q = -1.20\text{ MeV}$, বিক্রিয়াটি তাপহারী (Endothermic / Endoergic)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5277,12 +4996,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় ক্ষয় ধ্রুবক ও অর্ধায়ু (সমস্যা 32)</t>
+          <t>উন্নত নিউক্লীয় বিক্রিয়া, শক্তি ও ফিশন-ফিউশন (Nuclear Reactions &amp; Q-Value)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5290,31 +5009,26 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>##PRESET:decay-curve[size:medium]##
-[সমস্যা 32: তেজস্ক্রিয় ক্ষয় ধ্রুবক ও অর্ধায়ু]
-##PRESET:decay-curve[size:medium]##
-একটি তেজস্ক্রিয় আইসোটোপের অর্ধায়ু $T_{1/2} = 5.0\text{ দিন}$। মৌলটির ক্ষয় ধ্রুবক ($\lambda$) কত এবং কত দিন পর প্রাথমিক তেজস্ক্রিয় পরমাণুর মাত্র $6.25\%$ অবশিষ্ট থাকবে?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+উপরের তাপহারী বিক্রিয়াটি ঘটাতে আপতিত আলফা কণার ন্যূনতম গতিশক্তি (Threshold Kinetic Energy $K_{\text{th}}$) কত হতে হবে? ($K_{\text{th}} = |Q|\left(1 + rac{m_a}{m_X}+ight)$)।</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:decay-curve[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 32)।</t>
+          <t>ভরবেগের নিত্যতার কারণে উৎপন্ন কণাগুলো কিছু গতিশক্তি নিয়ে ছিটকে যায়, ফলে সমস্ত গতিশক্তি অভ্যন্তরীণ শক্তিতে রূপান্তরিত হতে পারে না। সূচনা শক্তি সমীকরণ: $K_{\text{th}} = |Q|\left(1 + \frac{m_\alpha}{m_N}\right) = 1.2016\left(1 + \frac{4}{14}\right) = 1.2016\left(\frac{18}{14}\right) = 1.2016 \times 1.2857 \approx 1.545\text{ MeV}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>ন্যূনতম গতিশক্তি $K_{\text{th}} = 1.54\text{ MeV}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5334,38 +5048,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>হাইড্রোজেন বর্ণালীর বামার ও লাইম্যান সিরিজ (সমস্যা 33)</t>
+          <t>উন্নত নিউক্লীয় বিক্রিয়া, শক্তি ও ফিশন-ফিউশন (Nuclear Reactions &amp; Q-Value)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: হাইড্রোজেন বর্ণালীর বামার ও লাইম্যান সিরিজ]
-হাইড্রোজেনের একটি ইলেকট্রন $n = 6$ শক্তিস্তর হতে $n = 2$ স্তরে লাফ দিলে নির্গত ফোটনের তরঙ্গদৈর্ঘ্য কত হবে? (রিডবার্গ ধ্রুবক $R_H = 1.097 \times 10^7\text{ m}^{-1}$)</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি পারমাণবিক চুল্লির বৈদ্যুতিক ক্ষমতা $P = 300\text{ MW}$ এবং এর তাপীয় দক্ষতা $\eta = 30\%$। প্রতিটি $^{235}	ext{U}$ ফিশনে $200\text{ MeV}$ শক্তি নির্গত হলে চুল্লিটিতে প্রতিদিন কত গ্রাম ইউরেনিয়াম-২৩৫ ব্যবহৃত হয়?</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 33)।</t>
+          <t>মোট তাপীয় ক্ষমতা $P_{\text{th}} = \frac{P}{\eta} = \frac{300\text{ MW}}{0.30} = 1000\text{ MW} = 1.0 \times 10^9\text{ J/s}$। প্রতিদিনে মোট তাপ শক্তি $E = (1.0 \times 10^9) \times (24 \times 3600) = 8.64 \times 10^{13}\text{ J}$। ১টি ফিশনে শক্তি $= 200 \times 1.6 \times 10^{-11}\text{ J} = 3.20 \times 10^{-11}\text{ J}$। প্রতিদিনে ফিশন সংখ্যা $N = \frac{8.64 \times 10^{13}}{3.20 \times 10^{-11}} = 2.70 \times 10^{24}$ টি। ব্যবহৃত ভর $m = \frac{N}{N_A} \times 235 = \frac{2.70 \times 10^{24}}{6.022 \times 10^{23}} \times 235 \approx 4.4835 \times 235 \approx 1053.6\text{ g} \approx 1.05\text{ kg}$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>দৈনিক ইউরেনিয়াম ব্যবহার $m = 1051.7\text{ g} \approx 1.05\text{ kg}$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5385,12 +5099,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>নিউক্লিয়াসের বন্ধন শক্তি ও ভর ত্রুটি (সমস্যা 34)</t>
+          <t>উন্নত নিউক্লীয় বিক্রিয়া, শক্তি ও ফিশন-ফিউশন (Nuclear Reactions &amp; Q-Value)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5398,25 +5112,26 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: নিউক্লিয়াসের বন্ধন শক্তি ও ভর ত্রুটি]
-একটি হিলিয়াম নিউক্লিয়াসের (${}_2^4\text{He}$) ভর $4.0015\text{ u}$। দুটি প্রোটন ও দুটি নিউট্রনের মোট ভর $4.0319\text{ u}$ হলে ভর ত্রুটি এবং প্রতি নিউক্লিয়ন বন্ধন শক্তি কত মেগা-ইলেকট্রন ভোল্ট (MeV)? ($1\text{ u} = 931.5\text{ MeV}$)</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+সূর্যে প্রোটন-প্রোটন চক্রের মাধ্যমে চারটি হাইড্রোজেন পরমাণু যুক্ত হয়ে একটি হিলিয়াম নিউক্লিয়াস এবং দুটি পজিট্রন উৎপন্ন করে ($4 _1^1	ext{H} 	o _2^4	ext{He} + 2 e^+ + 2
+u_e$)। সূর্য প্রতি সেকেন্ডে $3.8 	imes 10^{26}\text{ W}$ শক্তি বিকিরণ করলে প্রতি সেকেন্ডে সূর্যের ভর কত বিলিয়ন কেজি হ্রাস পায়?</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 34)।</t>
+          <t>আইনস্টাইনের ভর-শক্তি সম্পর্ক: $\Delta E = \Delta m c^2 \implies \frac{\Delta m}{\Delta t} = \frac{P}{c^2}$। মান বসিয়ে: $\frac{\Delta m}{\Delta t} = \frac{3.8 \times 10^{26}\text{ W}}{(3.0 \times 10^8\text{ m/s})^2} = \frac{3.8 \times 10^{26}}{9.0 \times 10^{16}} \approx 4.222 \times 10^9\text{ kg/s} = 4.22\text{ মিলিয়ন টন/সেকেন্ড}$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>প্রতি সেকেন্ডে ভর হ্রাস $\Delta m = 4.22 \times 10^9\text{ kg} = 4.22\text{ বিলিয়ন কেজি/সেকেন্ড}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5436,38 +5151,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় নমুনার সক্রিয়তা (Activity) (সমস্যা 35)</t>
+          <t>উন্নত নিউক্লীয় বিক্রিয়া, শক্তি ও ফিশন-ফিউশন (Nuclear Reactions &amp; Q-Value)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: তেজস্ক্রিয় নমুনার সক্রিয়তা (Activity)]
-একটি তেজস্ক্রিয় নমুনার ক্ষয় ধ্রুবক $\lambda = 0.03\text{ s}^{-1}$ এবং এতে উপস্থিত অবিঘটিত পরমাণুর সংখ্যা $N = 8 \times 10^{18}$। নমুনাটির বর্তমান সক্রিয়তা কত কুরি (Curie)? ($1\text{ Ci} = 3.7 \times 10^{10}\text{ Bq}$)</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তেজস্ক্রিয় মৌলের অর্ধায়ু $T_1$ এবং অপর একটি মৌলের অর্ধায়ু $T_2$। প্রারম্ভে উভয়ের পরমাণু সংখ্যা সমান ছিল। কত সময় পর তাদের পরমাণু সংখ্যার অনুপাত $1 : e$ হবে?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 35)।</t>
+          <t>$\frac{N_1(t)}{N_2(t)} = \frac{N_0 e^{-\lambda_1 t}}{N_0 e^{-\lambda_2 t}} = e^{(\lambda_2 - \lambda_1)t} = e \implies (\lambda_2 - \lambda_1)t = 1 \implies t = \frac{1}{\lambda_2 - \lambda_1}$। যেহেতু $\lambda = \frac{\ln 2}{T}$, তাই $t = \frac{1}{\frac{\ln 2}{T_2} - \frac{\ln 2}{T_1}} = \frac{T_1 T_2}{\ln 2(T_1 - T_2)}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>সময় $t = \frac{T_1 T_2}{\ln 2(T_1 - T_2)}$ (যেখানে $T_1 &gt; T_2$)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5487,12 +5202,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় গড় আয়ু ও অর্ধায়ু সম্পর্ক (সমস্যা 36)</t>
+          <t>উন্নত নিউক্লীয় বিক্রিয়া, শক্তি ও ফিশন-ফিউশন (Nuclear Reactions &amp; Q-Value)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5500,25 +5215,26 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: তেজস্ক্রিয় গড় আয়ু ও অর্ধায়ু সম্পর্ক]
-একটি তেজস্ক্রিয় রেডিয়াম নমুনার গড় আয়ু $\tau = 400\text{ বছর}$। এর অর্ধায়ু ($T_{1/2} = 0.693\tau$) কত বছর হবে?</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি নিউট্রন ক্ষয় হয়ে প্রোটন, ইলেকট্রন এবং অ্যান্টি-নিউট্রিনোতে পরিণত হয় ($n 	o p + e^- + ar{
+u}_e$)। এই ক্ষয় প্রক্রিয়ার নাম কী এবং নিউট্রিনোর অস্তিত্ব কেন পাউলি প্রস্তাব করেছিলেন?</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 36)।</t>
+          <t>যদি $\beta$-ক্ষয়ে কেবল প্রোটন ও ইলেকট্রন উৎপন্ন হতো, তবে দ্বি-কণা ভাঙনের কারণে নির্গত ইলেকট্রন নির্দিষ্ট একক শক্তি লাভ করত। কিন্তু বাস্তবে নির্গত ইলেকট্রনের শক্তি শূন্য হতে সর্বোচ্চ মান পর্যন্ত অবিচ্ছিন্ন থাকে। এই আপাত শক্তি ও স্পিন কৌণিক ভরবেগের অসঙ্গতি সমাধান করতে ১৯৩০ সালে ভোলফগ্যাং পাউলি একটি আধানহীন, প্রায় ভরহীন, স্পিন-১/২ কণা 'নিউট্রিনো' নিঃসরিত হওয়ার ভবিষ্যদ্বাণী করেন যা অবশিষ্ট শক্তি বহন করে নিয়ে যায়।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>বিটা ক্ষয় ($\beta^-$ decay); শক্তি ও কৌণিক ভরবেগের সংরক্ষণশীলতা নিশ্চিত করতে পাউলি নিউট্রিনো প্রস্তাব করেন</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5538,38 +5254,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>নিউক্লীয় ফিশন বিক্রিয়ায় শক্তি উৎপাদন (সমস্যা 37)</t>
+          <t>উন্নত নিউক্লীয় বিক্রিয়া, শক্তি ও ফিশন-ফিউশন (Nuclear Reactions &amp; Q-Value)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: নিউক্লীয় ফিশন বিক্রিয়ায় শক্তি উৎপাদন]
-একটি ইউরেনিয়াম (${}^{235}\text{U}$) নিউক্লিয়াসের ফিশনে প্রায় $200\text{ MeV}$ শক্তি নির্গত হয়। $1\text{ kg}$ ইউরেনিয়াম সম্পূর্ণ ফিশনে মোট কত জুল শক্তি পাওয়া যাবে?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+$_2^4	ext{He}$ নিউক্লিয়াসে দুটি প্রোটন পরস্পর হতে প্রায় $2.0\text{ fm}$ দূরে অবস্থান করে। এদের মধ্যকার কুলম্ব বিকর্ষণ বল কত নিউটন এবং এর ত্বরণ কত?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 37)।</t>
+          <t>কুলম্ব বল $F = \frac{k e^2}{r^2} = \frac{(9.0 \times 10^9) \times (1.6 \times 10^{-19})^2}{(2.0 \times 10^{-15})^2} = \frac{9.0 \times 10^9 \times 2.56 \times 10^{-38}}{4.0 \times 10^{-30}} = \frac{23.04 \times 10^{-29}}{4.0 \times 10^{-30}} = 57.6\text{ N}$। প্রোটনের ত্বরণ $a = \frac{F}{m_p} = \frac{57.6}{1.67 \times 10^{-27}} \approx 3.449 \times 10^{28}\text{ m/s}^2$। (সবল নিউক্লীয় বল এই বিশাল বিকর্ষণ বলকে পরাস্ত করে এদের আবদ্ধ রাখে)।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>বিকর্ষণ বল $F = 57.6\text{ N}$, প্রোটনের ত্বরণ $a \approx 3.45 \times 10^{28}\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5589,12 +5305,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>বোর কক্ষপথে ইলেকট্রনের বেগ ও দ্রুতি (সমস্যা 38)</t>
+          <t>উন্নত নিউক্লীয় বিক্রিয়া, শক্তি ও ফিশন-ফিউশন (Nuclear Reactions &amp; Q-Value)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5602,25 +5318,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: বোর কক্ষপথে ইলেকট্রনের বেগ ও দ্রুতি]
-হাইড্রোজেন পরমাণুর ১ম কক্ষপথে ইলেকট্রনের দ্রুতি $v_1 = 2.18 \times 10^6\text{ m/s}$ হলে 6-তম কক্ষপথে ইলেকট্রনের দ্রুতি ($v_n = v_1/n$) এবং প্রতি সেকেন্ডে ঘূর্ণন সংখ্যা কত?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি রেডিও-আইসোটোপের ভর $1.0\text{ }\mu	ext{g}$ এবং অর্ধায়ু $60\text{ দিন}$। আইসোটোপটির পারমাণবিক ভর $60\text{ g/mol}$ হলে নমুনাটির সক্রিয়তা কত কুরি ($	ext{Ci}$)?</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 38)।</t>
+          <t>পরমাণু সংখ্যা $N = \frac{10^{-6}\text{ g}}{60} \times (6.022 \times 10^{23}) \approx 1.0037 \times 10^{16}$ টি। অর্ধায়ু $T_{1/2} = 60 \times 86400 = 5.184 \times 10^6\text{ s}$। ক্ষয় ধ্রুবক $\lambda = \frac{0.69315}{5.184 \times 10^6} \approx 1.337 \times 10^{-7}\text{ s}^{-1}$। সক্রিয়তা $A = \lambda N = (1.337 \times 10^{-7}) \times (1.0037 \times 10^{16}) \approx 1.342 \times 10^{12}\text{ Bq}$। কুরিতে: $A = \frac{1.342 \times 10^{12}}{3.7 \times 10^{10}} \approx 36.27\text{ Ci}$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>সক্রিয়তা $A = 39.8\text{ Ci}$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5640,38 +5356,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় আলফা ও বিটা ক্ষয় সমীকরণ (সমস্যা 39)</t>
+          <t>উন্নত নিউক্লীয় বিক্রিয়া, শক্তি ও ফিশন-ফিউশন (Nuclear Reactions &amp; Q-Value)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: তেজস্ক্রিয় আলফা ও বিটা ক্ষয় সমীকরণ]
-একটি তেজস্ক্রিয় রেডিয়াম নিউক্লিয়াস (${}^{226}_{88}\text{Ra}$) হতে একটি $\alpha$-কণা এবং দুটি $\beta$-কণা নির্গত হলে নতুন উৎপন্ন নিউক্লিয়াসের পারমাণবিক সংখ্যা ও ভর সংখ্যা কত হবে?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি নিউক্লিয়ার ফিউশন বিক্রিয়ায় প্রয়োজনীয় উচ্চ তাপমাত্রা ($T \sim 10^7-10^8\text{ K}$) কেন প্রয়োজন হয় যাকে তাপ-নিউক্লীয় বিক্রিয়া (Thermonuclear reaction) বলে?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 39)।</t>
+          <t>দুটি ধনাত্মক নিউক্লিয়াসকে $10^{-15}\text{ m}$ কাছে আনতে কুলম্ব বিকর্ষণ বলকে অতিক্রম করতে হয়। এই কুলম্ব বিভব বাধার উচ্চতা প্রায় কয়েকশত $\text{keV}$। কেবলমাত্র কোটি কোটি কেলভিন উচ্চ তাপমাত্রায় তাপীয় গতিশক্তি ($K \sim k_B T$) এবং কোয়ান্টাম টানেলিং-এর মাধ্যমে নিউক্লিয়াসগুলো এই বাধা অতিক্রম করে সবল নিউক্লীয় বলের সীমার মধ্যে প্রবেশ করে ফিউশন ঘটাতে পারে।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>ধনাত্মক আধানযুক্ত দুটি নিউক্লিয়াসের মধ্যকার শক্তিশালী কুলম্ব বিকর্ষণ বিভব বাধা (Coulomb barrier) অতিক্রম করতে প্রচণ্ড গতিশক্তি প্রয়োজন</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5691,12 +5407,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>নিউক্লীয় ফিউশন ও নক্ষত্রের সৌর শক্তি (সমস্যা 40)</t>
+          <t>উন্নত নিউক্লীয় বিক্রিয়া, শক্তি ও ফিশন-ফিউশন (Nuclear Reactions &amp; Q-Value)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5704,25 +5420,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: নিউক্লীয় ফিউশন ও নক্ষত্রের সৌর শক্তি]
-সূর্যের অভ্যন্তরে ৪টি প্রোটন যুক্ত হয়ে ১টি হিলিয়াম নিউক্লিয়াস তৈরির সময় প্রায় $26.7\text{ MeV}$ শক্তি নির্গত হয়। প্রতি গ্রাম হাইড্রোজেন ফিউশনে কী পরিমাণ শক্তি নির্গত হবে?</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+তেজস্ক্রিয় বর্জ্যের দীর্ঘস্থায়ী বিপদ: প্লুটোনিয়াম-২৩৯ ($^{239}	ext{Pu}$)-এর অর্ধায়ু $24100\text{ বছর}$। এর তেজস্ক্রিয়তা নিরাপদ পর্যায়ে অর্থাৎ প্রারম্ভিক সক্রিয়তার $0.1\%$ (এক-সহস্রাংশ)-এ নেমে আসতে কত বছর সময় লাগবে?</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 40)।</t>
+          <t>$A/A_0 = 0.001 \implies e^{-\lambda t} = 0.001 \implies \lambda t = \ln(1000) \approx 6.9078$। অর্ধায়ু $T_{1/2} = 24100\text{ yr}$। সময় $t = \frac{6.9078}{\lambda} = \frac{6.9078}{0.69315} \times 24100 \approx 9.9658 \times 24100 \approx 240176\text{ বছর}$। এ কারণেই পারমাণবিক বর্জ্য ব্যবস্থাপনা মানব ইতিহাসের অন্যতম দীর্ঘস্থায়ী ভূ-প্রকৌশলগত চ্যালেঞ্জ।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>সময় $t = 240167\text{ বছর} \approx 2.40 \times 10^5\text{ বছর}$ (প্রায় আড়াই লক্ষ বছর)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5742,44 +5458,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>বোর পরমাণু মডেল ও কক্ষপথের শক্তি (সমস্যা 41)</t>
+          <t>উন্নত নিউক্লীয় পদার্থবিজ্ঞান সংশ্লেষণ ও প্রতিপাদন (Nuclear Physics Synthesis)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>##PRESET:bohr-atom[size:medium]##
-[সমস্যা 41: বোর পরমাণু মডেল ও কক্ষপথের শক্তি]
-##PRESET:bohr-atom[size:medium]##
-হাইড্রোজেন পরমাণুর ভূমিস্তরের শক্তি $E_1 = -13.6\text{ eV}$। বোরের স্বীকার্যানুসারে 4-তম কক্ষপথের শক্তি ($E_n = E_1/n^2$) এবং কক্ষপথের ব্যাসার্ধ ($r_n = n^2 r_1$) কত? ($r_1 = 0.53\text{ \AA}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+হাইড্রোজেন পরমাণুর বোর মডেলের ভিত্তিতে রিডবার্গ ধ্রুবকের তাত্ত্বিক রাশিমালা $R_H = rac{m e^4}{8 \epsilon_0^2 c h^3}$ প্রতিপাদন কর।</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##PRESET:bohr-atom[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 41)।</t>
+          <t>কক্ষীয় শক্তি $E_n = -\frac{m e^4}{8 \epsilon_0^2 h^2 n^2}$। দুটি স্তরের রূপান্তরে ফোটন শক্তি $\Delta E = E_{n2} - E_{n1} = \frac{h c}{\lambda} \implies \frac{1}{\lambda} = \frac{m e^4}{8 \epsilon_0^2 c h^3}\left(\frac{1}{n_1^2} - \frac{1}{n_2^2}\right)$। রিডবার্গ সূত্রের সাথে তুলনা করে: $R_H = \frac{m e^4}{8 \epsilon_0^2 c h^3}$। মান বসালে নিখুঁতভাবে $1.097 \times 10^7\text{ m}^{-1}$ পাওয়া যায়।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>$R_H = \frac{m e^4}{8 \epsilon_0^2 c h^3} \approx 1.097 \times 10^7\text{ m}^{-1}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5799,12 +5509,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় ক্ষয় ধ্রুবক ও অর্ধায়ু (সমস্যা 42)</t>
+          <t>উন্নত নিউক্লীয় পদার্থবিজ্ঞান সংশ্লেষণ ও প্রতিপাদন (Nuclear Physics Synthesis)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5812,31 +5522,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>##PRESET:decay-curve[size:medium]##
-[সমস্যা 42: তেজস্ক্রিয় ক্ষয় ধ্রুবক ও অর্ধায়ু]
-##PRESET:decay-curve[size:medium]##
-একটি তেজস্ক্রিয় আইসোটোপের অর্ধায়ু $T_{1/2} = 5.0\text{ দিন}$। মৌলটির ক্ষয় ধ্রুবক ($\lambda$) কত এবং কত দিন পর প্রাথমিক তেজস্ক্রিয় পরমাণুর মাত্র $6.25\%$ অবশিষ্ট থাকবে?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি রেডিও-আইসোটোপের সক্রিয়তা সময়ের সাথে গ্রাফ আঁকলে একটি এক্সপোনেনশিয়াল রেখা পাওয়া যায়। $\ln(A)$ বনাম সময় $t$-এর লেখচিত্রের প্রকৃতি এবং ঢাল কী নির্দেশ করে?</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>##PRESET:decay-curve[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 42)।</t>
+          <t>সক্রিয়তা সূত্র: $A(t) = A_0 e^{-\lambda t}$। উভয়পক্ষে প্রাকৃতিক লগারিদম নিয়ে: $\ln(A) = \ln(A_0) - \lambda t = (-\lambda)t + \ln(A_0)$। এটি $y = mx + c$ আকারের সরলরেখা। অতএব লেখচিত্রের ঢাল $m = -\lambda$, অর্থাৎ ঢালের মান হতে সরাসরি তেজস্ক্রিয় অবক্ষয় ধ্রুবক নির্ণয় করা যায়।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>এটি একটি নিম্নগামী সরলরেখা যার ঋণাত্মক ঢাল সরাসরি অবক্ষয় ধ্রুবক $-\lambda$ নির্দেশ করে</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5856,38 +5560,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>হাইড্রোজেন বর্ণালীর বামার ও লাইম্যান সিরিজ (সমস্যা 43)</t>
+          <t>উন্নত নিউক্লীয় পদার্থবিজ্ঞান সংশ্লেষণ ও প্রতিপাদন (Nuclear Physics Synthesis)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: হাইড্রোজেন বর্ণালীর বামার ও লাইম্যান সিরিজ]
-হাইড্রোজেনের একটি ইলেকট্রন $n = 6$ শক্তিস্তর হতে $n = 2$ স্তরে লাফ দিলে নির্গত ফোটনের তরঙ্গদৈর্ঘ্য কত হবে? (রিডবার্গ ধ্রুবক $R_H = 1.097 \times 10^7\text{ m}^{-1}$)</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি পরমাণুতে একটি ইলেকট্রন $n = 3$ স্তর হতে সরাসরি $n = 1$ স্তরে লাফ দিলে নির্গত ফোটনের রৈখিক ভরবেগ এবং পরমাণুর প্রতিক্ষেপ বেগ (Recoil velocity) কত? ($m_H = 1.67 	imes 10^{-27}\text{ kg}$)।</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 43)।</t>
+          <t>শক্তি পরিবর্তন $\Delta E = 13.6\left(1 - \frac{1}{9}\right) = 13.6 \times \frac{8}{9} \approx 12.089\text{ eV} = 1.934 \times 10^{-18}\text{ J}$। ফোটনের ভরবেগ $p = \frac{\Delta E}{c} = \frac{1.934 \times 10^{-18}}{3.0 \times 10^8} \approx 6.447 \times 10^{-27}\text{ kg}\cdot\text{m/s}$। ভরবেগ সংরক্ষণে পরমাণুর প্রতিক্ষেপ ভরবেগ সমান: $M v_{\text{recoil}} = p \implies v_{\text{recoil}} = \frac{6.447 \times 10^{-27}}{1.67 \times 10^{-27}} \approx 3.86\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>ফোটনের ভরবেগ $p = 6.45 \times 10^{-27}\text{ kg}\cdot\text{m/s}$, পরমাণুর প্রতিক্ষেপ বেগ $v_{\text{recoil}} = 3.86\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5907,12 +5611,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>নিউক্লিয়াসের বন্ধন শক্তি ও ভর ত্রুটি (সমস্যা 44)</t>
+          <t>উন্নত নিউক্লীয় পদার্থবিজ্ঞান সংশ্লেষণ ও প্রতিপাদন (Nuclear Physics Synthesis)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5920,25 +5624,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: নিউক্লিয়াসের বন্ধন শক্তি ও ভর ত্রুটি]
-একটি হিলিয়াম নিউক্লিয়াসের (${}_2^4\text{He}$) ভর $4.0015\text{ u}$। দুটি প্রোটন ও দুটি নিউট্রনের মোট ভর $4.0319\text{ u}$ হলে ভর ত্রুটি এবং প্রতি নিউক্লিয়ন বন্ধন শক্তি কত মেগা-ইলেকট্রন ভোল্ট (MeV)? ($1\text{ u} = 931.5\text{ MeV}$)</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+পজিট্রনিয়াম (Positronium) হলো একটি ইলেকট্রন ও একটি পজিট্রনের পারস্পরিক ঘূর্ণন ব্যবস্থা। হ্রাসকৃত ভর (Reduced mass $\mu = m_e/2$) ব্যবহার করে প্রমাণ কর যে পজিট্রনিয়ামের বোর ব্যাসার্ধ সাধারণ হাইড্রোজেন পরমাণুর দ্বিগুণ এবং শক্তি অর্ধেক।</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 44)।</t>
+          <t>সমতুল্য হ্রাসকৃত ভর $\mu = \frac{m_e \times m_e}{m_e + m_e} = \frac{m_e}{2}$। বোর ব্যাসার্ধ $r \propto \frac{1}{\mu} \implies r_{\text{Ps}} = 2 r_{\text{H}}$। কক্ষীয় শক্তি $E \propto \mu \implies E_{\text{Ps}} = \frac{1}{2} E_{\text{H}}$। ফলে ভূমি স্তরের শক্তি $-13.6/2 = -6.80\text{ eV}$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>$r_n(\text{Ps}) = 2 r_n(\text{H})$, $E_n(\text{Ps}) = \frac{1}{2}E_n(\text{H})$ (যেমন ভূমি অবস্থা $E_1 = -6.80\text{ eV}$)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5958,38 +5662,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় নমুনার সক্রিয়তা (Activity) (সমস্যা 45)</t>
+          <t>উন্নত নিউক্লীয় পদার্থবিজ্ঞান সংশ্লেষণ ও প্রতিপাদন (Nuclear Physics Synthesis)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: তেজস্ক্রিয় নমুনার সক্রিয়তা (Activity)]
-একটি তেজস্ক্রিয় নমুনার ক্ষয় ধ্রুবক $\lambda = 0.03\text{ s}^{-1}$ এবং এতে উপস্থিত অবিঘটিত পরমাণুর সংখ্যা $N = 4 \times 10^{18}$। নমুনাটির বর্তমান সক্রিয়তা কত কুরি (Curie)? ($1\text{ Ci} = 3.7 \times 10^{10}\text{ Bq}$)</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি রেডিও-আইসোটোপ প্রতি সেকেন্ডে $3.7 	imes 10^7$ টি $lpha$-কণা বিকিরণ করে ($1.0\text{ mCi}$)। প্রতিটি $lpha$-কণার শক্তি $5.0\text{ MeV}$ হলে প্রতি সেকেন্ডে নমুনাটি কত ওয়াট তাপ শক্তি নির্গত করে?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 45)।</t>
+          <t>১টি কণার শক্তি $E_\alpha = 5.0 \times 10^6 \times 1.6 \times 10^{-19}\text{ J} = 8.0 \times 10^{-13}\text{ J}$। প্রতি সেকেন্ডে মোট শক্তি $P = (3.7 \times 10^7\text{ s}^{-1}) \times (8.0 \times 10^{-13}\text{ J}) = 2.96 \times 10^{-5}\text{ W} = 29.6\text{ }\mu\text{W}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>তাপ উৎপাদন ক্ষমতা $P = 2.96 \times 10^{-5}\text{ W} = 29.6\text{ }\mu\text{W}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6009,12 +5713,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় গড় আয়ু ও অর্ধায়ু সম্পর্ক (সমস্যা 46)</t>
+          <t>উন্নত নিউক্লীয় পদার্থবিজ্ঞান সংশ্লেষণ ও প্রতিপাদন (Nuclear Physics Synthesis)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -6022,25 +5726,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: তেজস্ক্রিয় গড় আয়ু ও অর্ধায়ু সম্পর্ক]
-একটি তেজস্ক্রিয় রেডিয়াম নমুনার গড় আয়ু $\tau = 400\text{ বছর}$। এর অর্ধায়ু ($T_{1/2} = 0.693\tau$) কত বছর হবে?</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+মোজলের সূত্র (Moseley's Law) $\sqrt{f} = a(Z - b)$ বলতে কী বোঝায় এবং পর্যায় সারণির পারমাণবিক ভরের পরিবর্তে পারমাণবিক সংখ্যার ভিত্তিতে পুনর্গঠনে এর ভূমিকা কী ছিল?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 46)।</t>
+          <t>হেনরি মোজলে বিভিন্ন মৌলের $K_\alpha$ এক্স-রে বর্ণালী পরীক্ষা করে দেখান যে $\sqrt{f} \propto (Z - 1)$। এটি অকাট্যভাবে প্রমাণ করে যে পর্যায় সারণির ক্রম পারমাণবিক ভরের ওপর নয় বরং নিউক্লিয়াসে উপস্থিত প্রোটন সংখ্যা বা পারমাণবিক সংখ্যা $Z$-এর ওপর নিয়ন্ত্রিত। এর ফলেই মেন্ডেলিফের সারণির অসংগতিগুলো (যেমন আরগন-পটাশিয়াম, কোবাল্ট-নিকেল) স্থায়ীভাবে সমাধান হয়।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>বৈশিষ্ট্যমূলক এক্স-রের কম্পাঙ্কের বর্গমূল পারমাণবিক সংখ্যা $Z$-এর সমানুপাতিক; এটি প্রমাণ করে পারমাণবিক সংখ্যাই মৌলের মৌলিক সত্তা</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6060,38 +5764,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>নিউক্লীয় ফিশন বিক্রিয়ায় শক্তি উৎপাদন (সমস্যা 47)</t>
+          <t>উন্নত নিউক্লীয় পদার্থবিজ্ঞান সংশ্লেষণ ও প্রতিপাদন (Nuclear Physics Synthesis)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: নিউক্লীয় ফিশন বিক্রিয়ায় শক্তি উৎপাদন]
-একটি ইউরেনিয়াম (${}^{235}\text{U}$) নিউক্লিয়াসের ফিশনে প্রায় $200\text{ MeV}$ শক্তি নির্গত হয়। $1\text{ kg}$ ইউরেনিয়াম সম্পূর্ণ ফিশনে মোট কত জুল শক্তি পাওয়া যাবে?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি আলফা ক্ষয়ে নির্গত $lpha$-কণার গতিশক্তি $K_lpha$ এবং অবশিষ্ট প্রতিক্ষিপ্ত নিউক্লিয়াসের গতিশক্তি $K_R$-এর অনুপাত ভর সংখ্যা $A$-এর মাধ্যমে নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 47)।</t>
+          <t>ভরবেগ সংরক্ষণ: $p_\alpha = p_R = p$। গতিশক্তি $K = \frac{p^2}{2m}$। $\frac{K_\alpha}{K_R} = \frac{m_R}{m_\alpha} = \frac{A - 4}{4}$। মোট শক্তি $Q = K_\alpha + K_R = K_\alpha\left(1 + \frac{4}{A-4}\right) = K_\alpha\left(\frac{A}{A-4}\right) \implies K_\alpha = \frac{A-4}{A} Q$। ভারী নিউক্লিয়াসের ক্ষেত্রে ($A \approx 200$) নির্গত $\alpha$-কণাই মোট শক্তির প্রায় $98\%$ শক্তি বহন করে নিয়ে যায়।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>$K_\alpha = \frac{A - 4}{A} Q$, $K_R = \frac{4}{A} Q$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6111,12 +5815,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>বোর কক্ষপথে ইলেকট্রনের বেগ ও দ্রুতি (সমস্যা 48)</t>
+          <t>উন্নত নিউক্লীয় পদার্থবিজ্ঞান সংশ্লেষণ ও প্রতিপাদন (Nuclear Physics Synthesis)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6124,25 +5828,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: বোর কক্ষপথে ইলেকট্রনের বেগ ও দ্রুতি]
-হাইড্রোজেন পরমাণুর ১ম কক্ষপথে ইলেকট্রনের দ্রুতি $v_1 = 2.18 \times 10^6\text{ m/s}$ হলে 6-তম কক্ষপথে ইলেকট্রনের দ্রুতি ($v_n = v_1/n$) এবং প্রতি সেকেন্ডে ঘূর্ণন সংখ্যা কত?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+সূর্যে প্রতি সেকেন্ডে ফিউশন বিক্রিয়ায় প্রায় $6.0 	imes 10^{11}\text{ kg}$ হাইড্রোজেন হিলিয়ামে রূপান্তরিত হয়। সূর্যের বর্তমান ভর $2.0 	imes 10^{30}\text{ kg}$ হলে সূর্যের হাইড্রোজেন জ্বালানি শেষ হতে আরও কত বিলিয়ন বছর সময় লাগবে? (ধরি সূর্যের ভরের ১০% কোর অঞ্চলে ফিউশনে অংশ নেয়)।</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 48)।</t>
+          <t>উপলব্ধ হাইড্রোজেনের ভর $M = 0.10 \times (2.0 \times 10^{30}\text{ kg}) = 2.0 \times 10^{29}\text{ kg}$। ব্যবহারের হার $\frac{dM}{dt} = 6.0 \times 10^{11}\text{ kg/s}$। সময় $t = \frac{2.0 \times 10^{29}}{6.0 \times 10^{11}} \approx 3.333 \times 10^{17}\text{ s}$। বছরে রূপান্তর: $t = \frac{3.333 \times 10^{17}}{3.1536 \times 10^7} \approx 1.057 \times 10^{10}\text{ বছর} \approx 10.57\text{ বিলিয়ন বছর}$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>অবশিষ্ট জীবনকাল $\approx 10.57\text{ বিলিয়ন বছর} \approx 10\text{ বিলিয়ন বছর}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6162,38 +5866,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>তেজস্ক্রিয় আলফা ও বিটা ক্ষয় সমীকরণ (সমস্যা 49)</t>
+          <t>উন্নত নিউক্লীয় পদার্থবিজ্ঞান সংশ্লেষণ ও প্রতিপাদন (Nuclear Physics Synthesis)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: তেজস্ক্রিয় আলফা ও বিটা ক্ষয় সমীকরণ]
-একটি তেজস্ক্রিয় রেডিয়াম নিউক্লিয়াস (${}^{226}_{88}\text{Ra}$) হতে একটি $\alpha$-কণা এবং দুটি $\beta$-কণা নির্গত হলে নতুন উৎপন্ন নিউক্লিয়াসের পারমাণবিক সংখ্যা ও ভর সংখ্যা কত হবে?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+ইউরেনিয়াম ফিশন শৃঙ্খল বিক্রিয়ায় ক্রান্তীয় ভর (Critical Mass) এবং গুণন গুণক (Multiplication factor $k$) বলতে কী বোঝায়? পারমাণবিক বোমার ক্ষেত্রে $k$-এর মান কত হতে হয়?</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 49)।</t>
+          <t>ক্রান্তীয় ভর হলো ফিশনযোগ্য পদার্থের সেই ন্যূনতম ভর যাতে পৃষ্ঠ দিয়ে নিউট্রনের ক্ষয় চুল্লির ভেতর নিউট্রন উৎপাদনের সমান হয় ($k = 1$, সাব-ক্রিটিক্যাল $k &lt; 1$, সুপার-ক্রিটিক্যাল $k &gt; 1$)। পারমাণবিক বিদ্যুৎ কেন্দ্রে নিয়ন্ত্রণ দণ্ড দ্বারা $k = 1.0$ স্থির রেখে নিয়ন্ত্রিত শক্তি উৎপাদন করা হয়; কিন্তু পারমাণবিক অস্ত্রে ক্ষণিকের মধ্যে $k$-কে ১-এর চেয়ে অনেক বেশি ($k \gg 1$) করে অনিয়ন্ত্রিত বিস্ফোরণ ঘটানো হয়।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>$k = \frac{\text{বর্তমান প্রজন্মে ফিশন সৃষ্টিকারী নিউট্রন}}{\text{পূর্ববর্তী প্রজন্মের নিউট্রন}}$; সুপারক্রিটিক্যাল অবস্থায় $k &gt; 1$ (বোমায় $k \gg 1$)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6213,12 +5917,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>নিউক্লীয় ফিউশন ও নক্ষত্রের সৌর শক্তি (সমস্যা 50)</t>
+          <t>উন্নত নিউক্লীয় পদার্থবিজ্ঞান সংশ্লেষণ ও প্রতিপাদন (Nuclear Physics Synthesis)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6226,25 +5930,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: নিউক্লীয় ফিউশন ও নক্ষত্রের সৌর শক্তি]
-সূর্যের অভ্যন্তরে ৪টি প্রোটন যুক্ত হয়ে ১টি হিলিয়াম নিউক্লিয়াস তৈরির সময় প্রায় $26.7\text{ MeV}$ শক্তি নির্গত হয়। প্রতি গ্রাম হাইড্রোজেন ফিউশনে কী পরিমাণ শক্তি নির্গত হবে?</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+আইনস্টাইনের ভর-শক্তি সমীকরণ এবং ডাল্টনের ভর সংরক্ষণ নীতির সংমিশ্রণ: পারমাণবিক পদার্থবিজ্ঞানে কেন পৃথকভাবে ভর বা শক্তি সংরক্ষণশীল নয় বরং সমন্বিত 'ভর-শক্তি সংরক্ষণশীলতা' (Mass-Energy Conservation) নীতি সার্বজনীনভাবে প্রযোজ্য?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>বোর মডেল, রিডবার্গ সমীকরণ ও তেজস্ক্রিয় ক্ষয়সূত্রের সাহায্যে সমাধান (সমস্যা 50)।</t>
+          <t>চিরায়ত পদার্থবিজ্ঞানে ভর ও শক্তিকে পৃথক সংরক্ষিত সত্তা মনে করা হতো কারণ রাসায়নিক বিক্রিয়ায় ভর পরিবর্তন $\Delta m \sim 10^{-11}\text{ g}$ সাধারণ যন্ত্রে পরিমাপাতীত ছিল। কিন্তু পারমাণবিক নিউক্লিয়াসে বাইন্ডিং এনার্জি বা ভর ত্রুটি মোট ভরের প্রায় ০.১% থেকে ১% পর্যন্ত হয়, যা স্পষ্ট প্রদর্শন করে যে ভর কোনো অবিনশ্বর ধ্রুবক নয় বরং শক্তিরই একটি ঘনীভূত রূপ। ফলে সার্বজনীন প্রাকৃতিক নীতি হলো মোট ভর-শক্তির সমষ্টি সর্বদা সংরক্ষিত থাকে।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>পরমাণু ও নিউক্লিয়ার সমাধান 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>ভর এবং শক্তি একই মুদ্রার এপিঠ-ওপিঠ; রাসায়নিক ও পারমাণবিক উভয় বিক্রিয়াতেই ভর হ্রাস পেয়ে শক্তিতে এবং শক্তি কণিকায় রূপান্তরিত হতে পারে ($E = m c^2$)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
